--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.76155498287174</v>
+        <v>3.761554982871743</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.812309680332791</v>
+        <v>-4.812425050907562</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8906054823074185</v>
+        <v>0.8905593340775102</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3653638034057359</v>
+        <v>-0.3653749251521774</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.596667496710841</v>
+        <v>2.596660823662976</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-642.8%</t>
+          <t>-643.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.2%</t>
+          <t>-275.3%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.5%</t>
+          <t>-260.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.4%</t>
+          <t>-174.5%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46030,19 +46030,19 @@
         <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.118425199146975</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.4827698890543</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.205669422316712</v>
+        <v>1.324960819211508</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2515997785045487</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.84817393514945</v>
+        <v>2.967465332044246</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.118497600520387</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.485239595516106</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.204753941105402</v>
+        <v>1.324045338000198</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2540694849663548</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.846764512645779</v>
+        <v>2.966055909540575</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.129504522995089</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.553609781840116</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.1884127890505</v>
+        <v>1.307704185945296</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.86333685454221</v>
+        <v>2.982628251437005</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.119941231626981</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.66214796275625</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.135434225315938</v>
+        <v>1.254725622210733</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.853773563174101</v>
+        <v>2.973064960068897</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.944650796667367</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.693141122084955</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9477465266248424</v>
+        <v>1.067037923519638</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.678483128214488</v>
+        <v>2.797774525109284</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.949218028659155</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.517666862292486</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.022503462533618</v>
+        <v>1.141794859428413</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.683050360206276</v>
+        <v>2.802341757101071</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.924960057420362</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.628603114933735</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9538709902383251</v>
+        <v>1.073162387133121</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.658792388967483</v>
+        <v>2.778083785862278</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.928091442640268</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.831629692476969</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8757917444409373</v>
+        <v>0.9950831413357331</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.540107827661448</v>
+        <v>2.659399224556244</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.9382638290724</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.673704093541676</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9491343704471868</v>
+        <v>1.068425767341983</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.550280214093581</v>
+        <v>2.669571610988376</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.93321009964626</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.587460630515298</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9785780262315984</v>
+        <v>1.097869423126394</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.545226484667441</v>
+        <v>2.664517881562237</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.924985875090786</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.632767449914278</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9522310739165318</v>
+        <v>1.071522470811328</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4886305264826041</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.512516162306428</v>
+        <v>2.631807559201224</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.925537748123888</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.661800554616579</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9411697050687131</v>
+        <v>1.060461101963509</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4886305264826041</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.51306803533953</v>
+        <v>2.632359432234325</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.854810440015253</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.568990073165719</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9075665895404226</v>
+        <v>1.026857986435218</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3958200450317447</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.498027016101411</v>
+        <v>2.617318412996207</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.856683915939854</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.613379542495147</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8916842777332523</v>
+        <v>1.010975674628048</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4402095143611724</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.473266810428355</v>
+        <v>2.592558207323151</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.851759624451577</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.500708324258897</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9318284735394755</v>
+        <v>1.051119870434271</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3275382961249222</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.535945249881828</v>
+        <v>2.655236646776624</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.857250920282244</v>
       </c>
       <c r="D1949" t="n">
         <v>-4.388331323076224</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9822705698432119</v>
+        <v>1.101561966738008</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3275382961249222</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.541436545712496</v>
+        <v>2.660727942607291</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.868748122050783</v>
       </c>
       <c r="D1950" t="n">
         <v>-4.586565891962954</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9144739440570586</v>
+        <v>1.033765340951854</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5257728650116528</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.433993006148996</v>
+        <v>2.553284403043792</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.707103842051437</v>
       </c>
       <c r="D1951" t="n">
         <v>-4.669567172988233</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7196291516476003</v>
+        <v>0.8389205485423961</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.261206195433345</v>
+        <v>2.380497592328141</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.827253502770642</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.796634179295221</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7889520098440106</v>
+        <v>0.9082434067388063</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.381355856152551</v>
+        <v>2.500647253047346</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.841766528872965</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.883232762276324</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7688256027538924</v>
+        <v>0.8881169996486882</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.395868882254874</v>
+        <v>2.515160279149669</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.839185970215334</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.844849099718173</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7815985091195217</v>
+        <v>0.9008899060143174</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5059600869806754</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.416318521132133</v>
+        <v>2.535609918026929</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.835914999060636</v>
       </c>
       <c r="D1955" t="n">
         <v>-4.667732769683007</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8491740699788899</v>
+        <v>0.9684654668736856</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.5059600869806754</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.413047549977435</v>
+        <v>2.532338946872231</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.836598390822549</v>
       </c>
       <c r="D1956" t="n">
         <v>-4.638030645706714</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8617383113313206</v>
+        <v>0.9810297082261163</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5104302121959887</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.41104886661016</v>
+        <v>2.530340263504956</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.830385366128963</v>
       </c>
       <c r="D1957" t="n">
         <v>-4.458655224467946</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9272754551332421</v>
+        <v>1.046566852028038</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.35365345402527</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.498901896819006</v>
+        <v>2.618193293713801</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.811192821460553</v>
       </c>
       <c r="D1958" t="n">
         <v>-4.503669437988552</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8900772250565891</v>
+        <v>1.009368621951385</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3840023493398746</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.461500014961833</v>
+        <v>2.580791411856628</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.816884383799499</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.770673948260987</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7889669832865609</v>
+        <v>0.9082583801813566</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5783653873828232</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.350573754475009</v>
+        <v>2.469865151369805</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.816088305696</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.87187172969816</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7476917926081932</v>
+        <v>0.8669831895029889</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6467742009281424</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.308732388244319</v>
+        <v>2.428023785139115</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.813688267250317</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.839396143527388</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7582819886308187</v>
+        <v>0.8775733855256145</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6467742009281424</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.306332349798636</v>
+        <v>2.425623746693432</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.810212986458562</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.820358015820091</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7624219589219825</v>
+        <v>0.8817133558167782</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.704957812259337</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.267946902208164</v>
+        <v>2.38723829910296</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.987794855397242</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.851484646970709</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9275531754004158</v>
+        <v>1.046844572295212</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.704957812259337</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.445528771146845</v>
+        <v>2.56482016804164</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.988628184383376</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.903805027571501</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9074583521462327</v>
+        <v>1.026749749041028</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6700109522504648</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.467330216138302</v>
+        <v>2.586621613033097</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.994636714780302</v>
       </c>
       <c r="D1965" t="n">
         <v>-5.04812793349642</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8557377201731908</v>
+        <v>0.9750291170679866</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6700109522504648</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.473338746535227</v>
+        <v>2.592630143430023</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.073789362572324</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.900384963261417</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.993987556059214</v>
+        <v>1.11327895295401</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.5022035950155816</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.653175808668179</v>
+        <v>2.772467205562975</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.076582984103805</v>
       </c>
       <c r="D1967" t="n">
         <v>-5.002399645792639</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9559753045782065</v>
+        <v>1.075266701473002</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.5022035950155816</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.65596943019966</v>
+        <v>2.775260827094456</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.077245332495463</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.865790301698546</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011281390607502</v>
+        <v>1.130572787502298</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3655942509214892</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.738597385047774</v>
+        <v>2.85788878194257</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.076325809235573</v>
       </c>
       <c r="D1969" t="n">
         <v>-5.008555634521196</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9532557342185521</v>
+        <v>1.072547131113348</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.5083595837441396</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.652018662094294</v>
+        <v>2.77131005898909</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.142661363032394</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.946257635745074</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.044510487525822</v>
+        <v>1.163801884420617</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.5083595837441396</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.718354215891115</v>
+        <v>2.837645612785911</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.851242235421792</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.744467438079916</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8338074389812831</v>
+        <v>0.9530988358760788</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.3103413915749852</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.545746003582006</v>
+        <v>2.665037400476801</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.921532467743968</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.684576756437322</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9280539439604956</v>
+        <v>1.047345340855291</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2504507099323917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.651970644889737</v>
+        <v>2.771262041784533</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.936160203860011</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.782317301062297</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9035854622265496</v>
+        <v>1.022876859121345</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2663399880653719</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.657064814125992</v>
+        <v>2.776356211020788</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.934696184684683</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.958655061185226</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8315863390020495</v>
+        <v>0.9508777358968452</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4426777481883013</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.549798138876906</v>
+        <v>2.669089535771702</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.933187802724611</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.957965689024003</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8303537059064672</v>
+        <v>0.9496451028012629</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4426777481883013</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.548289756916835</v>
+        <v>2.667581153811631</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.933050670160048</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.964536654078596</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8275881873200663</v>
+        <v>0.9468795842148621</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.4492487132428942</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.544210045319516</v>
+        <v>2.663501442214312</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.933050670160048</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.956582683783823</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8307697754379753</v>
+        <v>0.950061172332771</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.4492487132428942</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.544210045319516</v>
+        <v>2.663501442214312</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.939432427187852</v>
       </c>
       <c r="D1978" t="n">
         <v>-4.946209307450737</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8413008829990147</v>
+        <v>0.9605922798938105</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.438875336909807</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.556815828147172</v>
+        <v>2.676107225041968</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.944324800562577</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.81852499765644</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8972669802914579</v>
+        <v>1.016558377186254</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.3111910271155105</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.638318787398475</v>
+        <v>2.757610184293271</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.931079473038449</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.879191588058829</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8597550166063748</v>
+        <v>0.9790464135011705</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3928893438340442</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.576054469843228</v>
+        <v>2.695345866738023</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.761554982871743</v>
+        <v>3.758018583433259</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.935177175649078</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.812425050907562</v>
+        <v>-4.814197728125183</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8905593340775102</v>
+        <v>1.009141660085257</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3653749251521774</v>
+        <v>-0.3660587292298888</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.596660823662976</v>
+        <v>2.715541938111145</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>28.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-30.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>452.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.0%</t>
+          <t>-654.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-275.3%</t>
+          <t>-291.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-174.5%</t>
+          <t>-186.4%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.118425199146975</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.4827698890543</v>
+        <v>-4.595036502193557</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.324960819211508</v>
+        <v>1.160762777061009</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2515997785045487</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.967465332044246</v>
+        <v>2.84817393514945</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.118497600520387</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.485239595516106</v>
+        <v>-4.597506208655363</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.324045338000198</v>
+        <v>1.159847295849699</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2540694849663548</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.966055909540575</v>
+        <v>2.846764512645779</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.129504522995089</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.553609781840116</v>
+        <v>-4.665876394979374</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.307704185945296</v>
+        <v>1.143506143794797</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.982628251437005</v>
+        <v>2.86333685454221</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.119941231626981</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.66214796275625</v>
+        <v>-4.774414575895507</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.254725622210733</v>
+        <v>1.090527580060235</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.973064960068897</v>
+        <v>2.853773563174101</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.944650796667367</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.693141122084955</v>
+        <v>-4.805407735224213</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.067037923519638</v>
+        <v>0.9028398813691392</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.797774525109284</v>
+        <v>2.678483128214488</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.949218028659155</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.517666862292486</v>
+        <v>-4.629933475431743</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.141794859428413</v>
+        <v>0.9775968172779148</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.802341757101071</v>
+        <v>2.683050360206276</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.924960057420362</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.628603114933735</v>
+        <v>-4.740869728072992</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.073162387133121</v>
+        <v>0.9089643449826224</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.778083785862278</v>
+        <v>2.658792388967483</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.928091442640268</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.831629692476969</v>
+        <v>-4.943896305616225</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9950831413357331</v>
+        <v>0.8308850991852346</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.659399224556244</v>
+        <v>2.540107827661448</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.78434395226416</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.9382638290724</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.673704093541676</v>
+        <v>-4.785970706680932</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.068425767341983</v>
+        <v>0.9042277251914843</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.669571610988376</v>
+        <v>2.550280214093581</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.93321009964626</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.587460630515298</v>
+        <v>-4.699727243654555</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.097869423126394</v>
+        <v>0.9336713809758956</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.664517881562237</v>
+        <v>2.545226484667441</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.924985875090786</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.632767449914278</v>
+        <v>-4.745034063053534</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.071522470811328</v>
+        <v>0.9073244286608293</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4886305264826041</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.631807559201224</v>
+        <v>2.512516162306428</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.925537748123888</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.661800554616579</v>
+        <v>-4.774067167755836</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.060461101963509</v>
+        <v>0.8962630598130104</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4886305264826041</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.632359432234325</v>
+        <v>2.51306803533953</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.854810440015253</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.568990073165719</v>
+        <v>-4.681256686304976</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.026857986435218</v>
+        <v>0.8626599442847198</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3958200450317447</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.617318412996207</v>
+        <v>2.498027016101411</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.856683915939854</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.613379542495147</v>
+        <v>-4.725646155634403</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.010975674628048</v>
+        <v>0.8467776324775498</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4402095143611724</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.592558207323151</v>
+        <v>2.473266810428355</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.851759624451577</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.500708324258897</v>
+        <v>-4.612974937398153</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.051119870434271</v>
+        <v>0.8869218282837728</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3275382961249222</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.655236646776624</v>
+        <v>2.535945249881828</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.857250920282244</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.388331323076224</v>
+        <v>-4.50059793621548</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.101561966738008</v>
+        <v>0.9373639245875092</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3275382961249222</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.660727942607291</v>
+        <v>2.541436545712496</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.868748122050783</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.586565891962954</v>
+        <v>-4.698832505102211</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.033765340951854</v>
+        <v>0.8695672988013559</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5257728650116528</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.553284403043792</v>
+        <v>2.433993006148996</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.707103842051437</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.669567172988233</v>
+        <v>-4.78183378612749</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8389205485423961</v>
+        <v>0.6747225063918976</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.380497592328141</v>
+        <v>2.261206195433345</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.827253502770642</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.796634179295221</v>
+        <v>-4.908900792434478</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9082434067388063</v>
+        <v>0.7440453645883081</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.500647253047346</v>
+        <v>2.381355856152551</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.841766528872965</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.883232762276324</v>
+        <v>-4.995499375415581</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8881169996486882</v>
+        <v>0.7239189574981899</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.515160279149669</v>
+        <v>2.395868882254874</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913419</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.839185970215334</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.844849099718173</v>
+        <v>-4.95711571285743</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9008899060143174</v>
+        <v>0.7366918638638189</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5059600869806754</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.535609918026929</v>
+        <v>2.416318521132133</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.835914999060636</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.667732769683007</v>
+        <v>-4.779999382822264</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9684654668736856</v>
+        <v>0.8042674247231874</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.5059600869806754</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.532338946872231</v>
+        <v>2.413047549977435</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.836598390822549</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.638030645706714</v>
+        <v>-4.75029725884597</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9810297082261163</v>
+        <v>0.8168316660756179</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5104302121959887</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.530340263504956</v>
+        <v>2.41104886661016</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.830385366128963</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.458655224467946</v>
+        <v>-4.570921837607202</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.046566852028038</v>
+        <v>0.8823688098775393</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.35365345402527</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.618193293713801</v>
+        <v>2.498901896819006</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.811192821460553</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.503669437988552</v>
+        <v>-4.615936051127809</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.009368621951385</v>
+        <v>0.8451705798008864</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3840023493398746</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.580791411856628</v>
+        <v>2.461500014961833</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.816884383799499</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.770673948260987</v>
+        <v>-4.882940561400244</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9082583801813566</v>
+        <v>0.7440603380308581</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5783653873828232</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.469865151369805</v>
+        <v>2.350573754475009</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.816088305696</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.87187172969816</v>
+        <v>-4.984138342837417</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8669831895029889</v>
+        <v>0.7027851473524904</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6467742009281424</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.428023785139115</v>
+        <v>2.308732388244319</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.813688267250317</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.839396143527388</v>
+        <v>-4.951662756666645</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8775733855256145</v>
+        <v>0.713375343375116</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6467742009281424</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.425623746693432</v>
+        <v>2.306332349798636</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.810212986458562</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.820358015820091</v>
+        <v>-4.932624628959347</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8817133558167782</v>
+        <v>0.71751531366628</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.704957812259337</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38723829910296</v>
+        <v>2.267946902208164</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.987794855397242</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.851484646970709</v>
+        <v>-4.963751260109966</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.046844572295212</v>
+        <v>0.8826465301447131</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.704957812259337</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.56482016804164</v>
+        <v>2.445528771146845</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.988628184383376</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.903805027571501</v>
+        <v>-5.016071640710758</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.026749749041028</v>
+        <v>0.86255170689053</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6700109522504648</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.586621613033097</v>
+        <v>2.467330216138302</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.994636714780302</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.04812793349642</v>
+        <v>-5.160394546635676</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9750291170679866</v>
+        <v>0.8108310749174885</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6700109522504648</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.592630143430023</v>
+        <v>2.473338746535227</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.073789362572324</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.900384963261417</v>
+        <v>-5.012651576400674</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.11327895295401</v>
+        <v>0.9490809108035112</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.5022035950155816</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.772467205562975</v>
+        <v>2.653175808668179</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.076582984103805</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.002399645792639</v>
+        <v>-5.114666258931895</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.075266701473002</v>
+        <v>0.9110686593225039</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.5022035950155816</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.775260827094456</v>
+        <v>2.65596943019966</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.077245332495463</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.865790301698546</v>
+        <v>-4.978056914837802</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.130572787502298</v>
+        <v>0.9663747453517992</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3655942509214892</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.85788878194257</v>
+        <v>2.738597385047774</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.076325809235573</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.008555634521196</v>
+        <v>-5.120822247660453</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.072547131113348</v>
+        <v>0.9083490889628494</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.5083595837441396</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.77131005898909</v>
+        <v>2.652018662094294</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.142661363032394</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.946257635745074</v>
+        <v>-5.05852424888433</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.163801884420617</v>
+        <v>0.999603842270119</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.5083595837441396</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.837645612785911</v>
+        <v>2.718354215891115</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.851242235421792</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.744467438079916</v>
+        <v>-4.856734051219172</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9530988358760788</v>
+        <v>0.7889007937255803</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.3103413915749852</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.665037400476801</v>
+        <v>2.545746003582006</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.921532467743968</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.684576756437322</v>
+        <v>-4.796843369576579</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.047345340855291</v>
+        <v>0.883147298704793</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2504507099323917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.771262041784533</v>
+        <v>2.651970644889737</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.936160203860011</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.782317301062297</v>
+        <v>-4.894583914201553</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.022876859121345</v>
+        <v>0.8586788169708468</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2663399880653719</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.776356211020788</v>
+        <v>2.657064814125992</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.934696184684683</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.958655061185226</v>
+        <v>-5.070921674324483</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9508777358968452</v>
+        <v>0.7866796937463469</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4426777481883013</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.669089535771702</v>
+        <v>2.549798138876906</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.933187802724611</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.957965689024003</v>
+        <v>-5.07023230216326</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9496451028012629</v>
+        <v>0.7854470606507644</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4426777481883013</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.667581153811631</v>
+        <v>2.548289756916835</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.933050670160048</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.964536654078596</v>
+        <v>-5.076803267217852</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9468795842148621</v>
+        <v>0.7826815420643638</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.4492487132428942</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.663501442214312</v>
+        <v>2.544210045319516</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.933050670160048</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.956582683783823</v>
+        <v>-5.06884929692308</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.950061172332771</v>
+        <v>0.7858631301822725</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.4492487132428942</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663501442214312</v>
+        <v>2.544210045319516</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.939432427187852</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.946209307450737</v>
+        <v>-5.058475920589993</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9605922798938105</v>
+        <v>0.796394237743312</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.438875336909807</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.676107225041968</v>
+        <v>2.556815828147172</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.944324800562577</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.81852499765644</v>
+        <v>-4.930791610795697</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.016558377186254</v>
+        <v>0.8523603350357554</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.3111910271155105</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.757610184293271</v>
+        <v>2.638318787398475</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.931079473038449</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.879191588058829</v>
+        <v>-4.991458201198085</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9790464135011705</v>
+        <v>0.814848371350672</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3928893438340442</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.695345866738023</v>
+        <v>2.576054469843228</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.758018583433259</v>
+        <v>3.569241358796967</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.935177175649078</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.814197728125183</v>
+        <v>-4.92646434126444</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.009141660085257</v>
+        <v>0.8449436179347589</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.3660587292298888</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.715541938111145</v>
+        <v>2.596250541216349</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-41.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.4%</t>
+          <t>454.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.2%</t>
+          <t>-649.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,32 +1140,32 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-291.7%</t>
+          <t>-289.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.6%</t>
+          <t>-263.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.4%</t>
+          <t>-176.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1981"/>
+  <dimension ref="A1:G1982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.595036502193557</v>
+        <v>-4.4827698890543</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.160762777061009</v>
+        <v>1.205669422316712</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2515997785045487</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.597506208655363</v>
+        <v>-4.485239595516106</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.159847295849699</v>
+        <v>1.204753941105402</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2540694849663548</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.665876394979374</v>
+        <v>-4.553609781840116</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.143506143794797</v>
+        <v>1.1884127890505</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2447937859301399</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.774414575895507</v>
+        <v>-4.66214796275625</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.090527580060235</v>
+        <v>1.135434225315938</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2447937859301399</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.805407735224213</v>
+        <v>-4.693141122084955</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9028398813691392</v>
+        <v>0.9477465266248424</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2447937859301399</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.629933475431743</v>
+        <v>-4.517666862292486</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9775968172779148</v>
+        <v>1.022503462533618</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2447937859301399</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.740869728072992</v>
+        <v>-4.628603114933735</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9089643449826224</v>
+        <v>0.9538709902383251</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2447937859301399</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.943896305616225</v>
+        <v>-4.831629692476969</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8308850991852346</v>
+        <v>0.8757917444409373</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.4478203634733733</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226416</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.785970706680932</v>
+        <v>-4.673704093541676</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9042277251914843</v>
+        <v>0.9491343704471868</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.4478203634733733</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.699727243654555</v>
+        <v>-4.587460630515298</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9336713809758956</v>
+        <v>0.9785780262315984</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.4478203634733733</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.745034063053534</v>
+        <v>-4.632767449914278</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9073244286608293</v>
+        <v>0.9522310739165318</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4886305264826041</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.774067167755836</v>
+        <v>-4.661800554616579</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8962630598130104</v>
+        <v>0.9411697050687131</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4886305264826041</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.681256686304976</v>
+        <v>-4.568990073165719</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8626599442847198</v>
+        <v>0.9075665895404226</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3958200450317447</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.725646155634403</v>
+        <v>-4.613379542495147</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8467776324775498</v>
+        <v>0.8916842777332523</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4402095143611724</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.612974937398153</v>
+        <v>-4.500708324258897</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8869218282837728</v>
+        <v>0.9318284735394755</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3275382961249222</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.50059793621548</v>
+        <v>-4.388331323076224</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9373639245875092</v>
+        <v>0.9822705698432119</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3275382961249222</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.698832505102211</v>
+        <v>-4.586565891962954</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8695672988013559</v>
+        <v>0.9144739440570586</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5257728650116528</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.78183378612749</v>
+        <v>-4.669567172988233</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6747225063918976</v>
+        <v>0.7196291516476003</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5443437495388266</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.908900792434478</v>
+        <v>-4.796634179295221</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7440453645883081</v>
+        <v>0.7889520098440106</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5443437495388266</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.995499375415581</v>
+        <v>-4.883232762276324</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7239189574981899</v>
+        <v>0.7688256027538924</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5443437495388266</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913419</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.95711571285743</v>
+        <v>-4.844849099718173</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7366918638638189</v>
+        <v>0.7815985091195217</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5059600869806754</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.779999382822264</v>
+        <v>-4.667732769683007</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8042674247231874</v>
+        <v>0.8491740699788899</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.5059600869806754</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793896</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.75029725884597</v>
+        <v>-4.638030645706714</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8168316660756179</v>
+        <v>0.8617383113313206</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5104302121959887</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.570921837607202</v>
+        <v>-4.458655224467946</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8823688098775393</v>
+        <v>0.9272754551332421</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.35365345402527</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.615936051127809</v>
+        <v>-4.503669437988552</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8451705798008864</v>
+        <v>0.8900772250565891</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3840023493398746</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.882940561400244</v>
+        <v>-4.770673948260987</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7440603380308581</v>
+        <v>0.7889669832865609</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5783653873828232</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.984138342837417</v>
+        <v>-4.87187172969816</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7027851473524904</v>
+        <v>0.7476917926081932</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6467742009281424</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.951662756666645</v>
+        <v>-4.839396143527388</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.713375343375116</v>
+        <v>0.7582819886308187</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6467742009281424</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.932624628959347</v>
+        <v>-4.820358015820091</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.71751531366628</v>
+        <v>0.7624219589219825</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.704957812259337</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.963751260109966</v>
+        <v>-4.851484646970709</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8826465301447131</v>
+        <v>0.9275531754004158</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.704957812259337</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.016071640710758</v>
+        <v>-4.903805027571501</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.86255170689053</v>
+        <v>0.9074583521462327</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6700109522504648</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.160394546635676</v>
+        <v>-5.04812793349642</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8108310749174885</v>
+        <v>0.8557377201731908</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6700109522504648</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.012651576400674</v>
+        <v>-4.900384963261417</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9490809108035112</v>
+        <v>0.993987556059214</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.5022035950155816</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.114666258931895</v>
+        <v>-5.002399645792639</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9110686593225039</v>
+        <v>0.9559753045782065</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.5022035950155816</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.978056914837802</v>
+        <v>-4.865790301698546</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9663747453517992</v>
+        <v>1.011281390607502</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3655942509214892</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.120822247660453</v>
+        <v>-5.008555634521196</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9083490889628494</v>
+        <v>0.9532557342185521</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.5083595837441396</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.05852424888433</v>
+        <v>-4.946257635745074</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.999603842270119</v>
+        <v>1.044510487525822</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.5083595837441396</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.856734051219172</v>
+        <v>-4.744467438079916</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7889007937255803</v>
+        <v>0.8338074389812831</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.3103413915749852</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.796843369576579</v>
+        <v>-4.684576756437322</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.883147298704793</v>
+        <v>0.9280539439604956</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2504507099323917</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.894583914201553</v>
+        <v>-4.782317301062297</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8586788169708468</v>
+        <v>0.9035854622265496</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2663399880653719</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.070921674324483</v>
+        <v>-4.958655061185226</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7866796937463469</v>
+        <v>0.8315863390020495</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4426777481883013</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.07023230216326</v>
+        <v>-4.957965689024003</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7854470606507644</v>
+        <v>0.8303537059064672</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4426777481883013</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024957</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.076803267217852</v>
+        <v>-4.964536654078596</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7826815420643638</v>
+        <v>0.8275881873200663</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.4492487132428942</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.06884929692308</v>
+        <v>-4.956582683783823</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7858631301822725</v>
+        <v>0.8307697754379753</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.4492487132428942</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.058475920589993</v>
+        <v>-4.946209307450737</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.796394237743312</v>
+        <v>0.8413008829990147</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.438875336909807</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.930791610795697</v>
+        <v>-4.81852499765644</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8523603350357554</v>
+        <v>0.8972669802914579</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.3111910271155105</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.991458201198085</v>
+        <v>-4.879191588058829</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.814848371350672</v>
+        <v>0.8597550166063748</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3928893438340442</v>
@@ -47108,22 +47108,45 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.569241358796967</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.92646434126444</v>
+        <v>-4.878790685442493</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8449436179347589</v>
+        <v>0.8640130802635375</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3660587292298888</v>
+        <v>-0.393055838655978</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.596250541216349</v>
+        <v>2.580052275560695</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="2" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B1982" t="n">
+        <v>3.760884783693838</v>
+      </c>
+      <c r="C1982" t="n">
+        <v>2.701899521690678</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>-4.878790685442493</v>
+      </c>
+      <c r="E1982" t="n">
+        <v>0.8640130802635375</v>
+      </c>
+      <c r="F1982" t="n">
+        <v>-0.393055838655978</v>
+      </c>
+      <c r="G1982" t="n">
+        <v>2.694963318677046</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-33.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.9%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.5%</t>
+          <t>-654.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.8%</t>
+          <t>-279.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-263.3%</t>
+          <t>-260.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.5%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.118425199146975</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.4827698890543</v>
+        <v>-4.598042673172121</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.205669422316712</v>
+        <v>1.278851705564379</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2515997785045487</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.84817393514945</v>
+        <v>2.967465332044246</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.118497600520387</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.485239595516106</v>
+        <v>-4.600512379633927</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.204753941105402</v>
+        <v>1.277936224353069</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2540694849663548</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.846764512645779</v>
+        <v>2.966055909540575</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.129504522995089</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.553609781840116</v>
+        <v>-4.668882565957937</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.1884127890505</v>
+        <v>1.261595072298167</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.86333685454221</v>
+        <v>2.982628251437005</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.119941231626981</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.66214796275625</v>
+        <v>-4.777420746874071</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.135434225315938</v>
+        <v>1.208616508563605</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.853773563174101</v>
+        <v>2.973064960068897</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.944650796667367</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.693141122084955</v>
+        <v>-4.808413906202777</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9477465266248424</v>
+        <v>1.02092880987251</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.678483128214488</v>
+        <v>2.797774525109284</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.949218028659155</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.517666862292486</v>
+        <v>-4.632939646410307</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.022503462533618</v>
+        <v>1.095685745781285</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.683050360206276</v>
+        <v>2.802341757101071</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.924960057420362</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.628603114933735</v>
+        <v>-4.743875899051556</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9538709902383251</v>
+        <v>1.027053273485993</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2447937859301399</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.658792388967483</v>
+        <v>2.778083785862278</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.928091442640268</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.831629692476969</v>
+        <v>-4.946902476594789</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8757917444409373</v>
+        <v>0.9489740276886049</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.540107827661448</v>
+        <v>2.659399224556244</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.9382638290724</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.673704093541676</v>
+        <v>-4.788976877659496</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9491343704471868</v>
+        <v>1.022316653694854</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.550280214093581</v>
+        <v>2.669571610988376</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.93321009964626</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.587460630515298</v>
+        <v>-4.702733414633118</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9785780262315984</v>
+        <v>1.051760309479266</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.4478203634733733</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.545226484667441</v>
+        <v>2.664517881562237</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.924985875090786</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.632767449914278</v>
+        <v>-4.748040234032098</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9522310739165318</v>
+        <v>1.025413357164199</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4886305264826041</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.512516162306428</v>
+        <v>2.631807559201224</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.925537748123888</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.661800554616579</v>
+        <v>-4.777073338734399</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9411697050687131</v>
+        <v>1.014351988316381</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4886305264826041</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.51306803533953</v>
+        <v>2.632359432234325</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.854810440015253</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.568990073165719</v>
+        <v>-4.68426285728354</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9075665895404226</v>
+        <v>0.98074887278809</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3958200450317447</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.498027016101411</v>
+        <v>2.617318412996207</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.856683915939854</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.613379542495147</v>
+        <v>-4.728652326612967</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8916842777332523</v>
+        <v>0.9648665609809199</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4402095143611724</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.473266810428355</v>
+        <v>2.592558207323151</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.851759624451577</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.500708324258897</v>
+        <v>-4.615981108376717</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9318284735394755</v>
+        <v>1.005010756787143</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3275382961249222</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.535945249881828</v>
+        <v>2.655236646776624</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.857250920282244</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.388331323076224</v>
+        <v>-4.503604107194044</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9822705698432119</v>
+        <v>1.055452853090879</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3275382961249222</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.541436545712496</v>
+        <v>2.660727942607291</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.868748122050783</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.586565891962954</v>
+        <v>-4.701838676080775</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9144739440570586</v>
+        <v>0.987656227304726</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5257728650116528</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.433993006148996</v>
+        <v>2.553284403043792</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.707103842051437</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.669567172988233</v>
+        <v>-4.784839957106054</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7196291516476003</v>
+        <v>0.7928114348952677</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.261206195433345</v>
+        <v>2.380497592328141</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.827253502770642</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.796634179295221</v>
+        <v>-4.911906963413042</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7889520098440106</v>
+        <v>0.8621342930916782</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.381355856152551</v>
+        <v>2.500647253047346</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.841766528872965</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.883232762276324</v>
+        <v>-4.998505546394145</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7688256027538924</v>
+        <v>0.8420078860015601</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5443437495388266</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.395868882254874</v>
+        <v>2.515160279149669</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.839185970215334</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.844849099718173</v>
+        <v>-4.960121883835994</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7815985091195217</v>
+        <v>0.8547807923671891</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5059600869806754</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.416318521132133</v>
+        <v>2.535609918026929</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.835914999060636</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.667732769683007</v>
+        <v>-4.783005553800828</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8491740699788899</v>
+        <v>0.9223563532265575</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.5059600869806754</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.413047549977435</v>
+        <v>2.532338946872231</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.836598390822549</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.638030645706714</v>
+        <v>-4.753303429824534</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8617383113313206</v>
+        <v>0.934920594578988</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5104302121959887</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.41104886661016</v>
+        <v>2.530340263504956</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.830385366128963</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.458655224467946</v>
+        <v>-4.573928008585766</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9272754551332421</v>
+        <v>1.000457738380909</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.35365345402527</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.498901896819006</v>
+        <v>2.618193293713801</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.811192821460553</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.503669437988552</v>
+        <v>-4.618942222106373</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8900772250565891</v>
+        <v>0.9632595083042566</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3840023493398746</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.461500014961833</v>
+        <v>2.580791411856628</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.816884383799499</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.770673948260987</v>
+        <v>-4.885946732378808</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7889669832865609</v>
+        <v>0.8621492665342283</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5783653873828232</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.350573754475009</v>
+        <v>2.469865151369805</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.816088305696</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.87187172969816</v>
+        <v>-4.987144513815981</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7476917926081932</v>
+        <v>0.8208740758558606</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6467742009281424</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.308732388244319</v>
+        <v>2.428023785139115</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.813688267250317</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.839396143527388</v>
+        <v>-4.954668927645208</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7582819886308187</v>
+        <v>0.8314642718784864</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6467742009281424</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.306332349798636</v>
+        <v>2.425623746693432</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.810212986458562</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.820358015820091</v>
+        <v>-4.935630799937911</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7624219589219825</v>
+        <v>0.8356042421696501</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.704957812259337</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.267946902208164</v>
+        <v>2.38723829910296</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.987794855397242</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.851484646970709</v>
+        <v>-4.96675743108853</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9275531754004158</v>
+        <v>1.000735458648083</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.704957812259337</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.445528771146845</v>
+        <v>2.56482016804164</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.988628184383376</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.903805027571501</v>
+        <v>-5.019077811689321</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9074583521462327</v>
+        <v>0.9806406353939003</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6700109522504648</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.467330216138302</v>
+        <v>2.586621613033097</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.994636714780302</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.04812793349642</v>
+        <v>-5.16340071761424</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8557377201731908</v>
+        <v>0.9289200034208585</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6700109522504648</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.473338746535227</v>
+        <v>2.592630143430023</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.073789362572324</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.900384963261417</v>
+        <v>-5.015657747379238</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.993987556059214</v>
+        <v>1.067169839306882</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.5022035950155816</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.653175808668179</v>
+        <v>2.772467205562975</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.076582984103805</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.002399645792639</v>
+        <v>-5.117672429910459</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9559753045782065</v>
+        <v>1.029157587825874</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.5022035950155816</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.65596943019966</v>
+        <v>2.775260827094456</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.077245332495463</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.865790301698546</v>
+        <v>-4.981063085816366</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011281390607502</v>
+        <v>1.084463673855169</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3655942509214892</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.738597385047774</v>
+        <v>2.85788878194257</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.076325809235573</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.008555634521196</v>
+        <v>-5.123828418639016</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9532557342185521</v>
+        <v>1.02643801746622</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.5083595837441396</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.652018662094294</v>
+        <v>2.77131005898909</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.142661363032394</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.946257635745074</v>
+        <v>-5.061530419862894</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.044510487525822</v>
+        <v>1.117692770773489</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.5083595837441396</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.718354215891115</v>
+        <v>2.837645612785911</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.851242235421792</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.744467438079916</v>
+        <v>-4.859740222197736</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8338074389812831</v>
+        <v>0.9069897222289507</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.3103413915749852</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.545746003582006</v>
+        <v>2.665037400476801</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.921532467743968</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.684576756437322</v>
+        <v>-4.799849540555143</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9280539439604956</v>
+        <v>1.001236227208163</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2504507099323917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.651970644889737</v>
+        <v>2.771262041784533</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.936160203860011</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.782317301062297</v>
+        <v>-4.897590085180117</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9035854622265496</v>
+        <v>0.976767745474217</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2663399880653719</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.657064814125992</v>
+        <v>2.776356211020788</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.934696184684683</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.958655061185226</v>
+        <v>-5.073927845303047</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8315863390020495</v>
+        <v>0.9047686222497169</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4426777481883013</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.549798138876906</v>
+        <v>2.669089535771702</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.933187802724611</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.957965689024003</v>
+        <v>-5.073238473141823</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8303537059064672</v>
+        <v>0.9035359891541348</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4426777481883013</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.548289756916835</v>
+        <v>2.667581153811631</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.933050670160048</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.964536654078596</v>
+        <v>-5.079809438196416</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8275881873200663</v>
+        <v>0.9007704705677337</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.4492487132428942</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.544210045319516</v>
+        <v>2.663501442214312</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.933050670160048</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.956582683783823</v>
+        <v>-5.071855467901644</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8307697754379753</v>
+        <v>0.9039520586856429</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.4492487132428942</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.544210045319516</v>
+        <v>2.663501442214312</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.939432427187852</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.946209307450737</v>
+        <v>-5.061482091568557</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8413008829990147</v>
+        <v>0.9144831662466824</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.438875336909807</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.556815828147172</v>
+        <v>2.676107225041968</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.944324800562577</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.81852499765644</v>
+        <v>-4.933797781774261</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8972669802914579</v>
+        <v>0.9704492635391255</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.3111910271155105</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.638318787398475</v>
+        <v>2.757610184293271</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.931079473038449</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.879191588058829</v>
+        <v>-4.994464372176649</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8597550166063748</v>
+        <v>0.9329372998540424</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3928893438340442</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.576054469843228</v>
+        <v>2.695345866738023</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.935177175649078</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.878790685442493</v>
+        <v>-4.929470512243004</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8640130802635375</v>
+        <v>0.9630325464381291</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.393055838655978</v>
+        <v>-0.3660587292298888</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.580052275560695</v>
+        <v>2.715541938111145</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.760884783693838</v>
+        <v>3.566240913644361</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.701899521690678</v>
+        <v>2.784485988342569</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.878790685442493</v>
+        <v>-4.929470512243004</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8640130802635375</v>
+        <v>0.9630325464381291</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.393055838655978</v>
+        <v>-0.3660587292298888</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.694963318677046</v>
+        <v>2.777549785328937</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-42.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.3%</t>
+          <t>454.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.5%</t>
+          <t>-650.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>129.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.9%</t>
+          <t>-290.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.6%</t>
+          <t>-153.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.6%</t>
+          <t>-266.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-177.1%</t>
         </is>
       </c>
     </row>
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.86915315329871</v>
+        <v>-10.94466591778702</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.186063682489628</v>
+        <v>-1.21626878828495</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.913663929842834</v>
+        <v>-2.97236357069436</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.413755645237905</v>
+        <v>1.378535860726989</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10118207303498</v>
+        <v>-11.17669483752328</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.276181521755019</v>
+        <v>-1.30638662755034</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.975676627031257</v>
+        <v>-3.034376267882783</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.379241755553966</v>
+        <v>1.34402197104305</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.04916655906616</v>
+        <v>-11.12467932355447</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.251384980481093</v>
+        <v>-1.281590086276414</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.975676627031257</v>
+        <v>-3.034376267882783</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.383232091240367</v>
+        <v>1.348012306729451</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19083840079028</v>
+        <v>-11.26635116527859</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.309528944069482</v>
+        <v>-1.339734049864804</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.975676627031257</v>
+        <v>-3.034376267882783</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.381756864341625</v>
+        <v>1.346537079830709</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14124755636545</v>
+        <v>-11.21676032085375</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.274639196134676</v>
+        <v>-1.304844301929997</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.926085782606423</v>
+        <v>-2.98478542345795</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.426564781161398</v>
+        <v>1.391344996650482</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.94209544912835</v>
+        <v>-11.01760821361665</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.20802948688652</v>
+        <v>-1.238234592681841</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.76076325665661</v>
+        <v>-2.819462897508136</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.512707163084603</v>
+        <v>1.477487378573687</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.71625029640894</v>
+        <v>-10.79176306089724</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.108112352762547</v>
+        <v>-1.138317458557867</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.718836581069446</v>
+        <v>-2.777536221920973</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.547442241473109</v>
+        <v>1.512222456962194</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.59167164007135</v>
+        <v>-10.66718440455965</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.057141745671451</v>
+        <v>-1.087346851466771</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.718836581069446</v>
+        <v>-2.777536221920973</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.548581386029168</v>
+        <v>1.513361601518252</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.64456692811564</v>
+        <v>-10.72007969260394</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.075666086727058</v>
+        <v>-1.105871192522379</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.713881234981</v>
+        <v>-2.772580875832527</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.554188367844344</v>
+        <v>1.518968583333428</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.36065819718689</v>
+        <v>-10.43617096167519</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9563688901169218</v>
+        <v>-0.9865739959122424</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.713881234981</v>
+        <v>-2.772580875832527</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.55992207208298</v>
+        <v>1.524702287572064</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.28929180457724</v>
+        <v>-10.36480456906554</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9375595954669285</v>
+        <v>-0.967764701262249</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.642514842371352</v>
+        <v>-2.701214483222878</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.593004645254904</v>
+        <v>1.557784860743988</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.02545493737317</v>
+        <v>-10.10096770186147</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.841908329898208</v>
+        <v>-0.8721134356935285</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.642514842371352</v>
+        <v>-2.701214483222878</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.583121163941996</v>
+        <v>1.54790137943108</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.758213136504772</v>
+        <v>-9.833725900993073</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7368461700502227</v>
+        <v>-0.7670512758455432</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.642514842371352</v>
+        <v>-2.701214483222878</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.581286603442623</v>
+        <v>1.546066818931707</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.660306097828281</v>
+        <v>-9.735818862316583</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.697983669553087</v>
+        <v>-0.728188775348408</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.574529092510796</v>
+        <v>-2.633228733362322</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.621777738385495</v>
+        <v>1.58655795387458</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.636352556852323</v>
+        <v>-9.711865321340625</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6877337470172105</v>
+        <v>-0.717938852812531</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.550575551534838</v>
+        <v>-2.609275192386364</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.636818369116564</v>
+        <v>1.601598584605648</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.372292618529526</v>
+        <v>-9.447805383017828</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5953700878498438</v>
+        <v>-0.6255751936451643</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.286515613212042</v>
+        <v>-2.345215254063568</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.781994015948489</v>
+        <v>1.746774231437573</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.665212995024689</v>
+        <v>-8.740725759512991</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3153252721082098</v>
+        <v>-0.3455303779035304</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.286515613212042</v>
+        <v>-2.345215254063568</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.779206982288188</v>
+        <v>1.743987197777272</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.625028696658498</v>
+        <v>-8.7005414611468</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2989079288738923</v>
+        <v>-0.3291130346692128</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.246331314845851</v>
+        <v>-2.305030955697378</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.803661185195744</v>
+        <v>1.768441400684828</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.544958901120694</v>
+        <v>-8.620471665608996</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2675131894380134</v>
+        <v>-0.2977182952333344</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.166261519308047</v>
+        <v>-2.224961160159574</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.851069883739183</v>
+        <v>1.815850099228268</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.311477678891094</v>
+        <v>-8.386990443379396</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1661962717083214</v>
+        <v>-0.1964013775036419</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.932780297078449</v>
+        <v>-1.991479937929975</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.999083045914795</v>
+        <v>1.963863261403879</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.16181128788358</v>
+        <v>-8.237324052371882</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1092219256182747</v>
+        <v>-0.1394270314135957</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.839876805835913</v>
+        <v>-1.898576446687439</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.051932930347357</v>
+        <v>2.016713145836442</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.029535814252693</v>
+        <v>-8.105048578740995</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06094424941889276</v>
+        <v>-0.09114935521421375</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.707601332205026</v>
+        <v>-1.766300973056552</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.126665701272916</v>
+        <v>2.091445916762001</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.83893613957954</v>
+        <v>-7.914448904067842</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01811068113800474</v>
+        <v>-0.01209442465731581</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.517001657531873</v>
+        <v>-1.5757012983834</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.243840566764445</v>
+        <v>2.208620782253529</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.589936340895959</v>
+        <v>-7.665449105384261</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.130616941835096</v>
+        <v>0.1004118360397754</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.517001657531873</v>
+        <v>-1.5757012983834</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.256746907988104</v>
+        <v>2.221527123477188</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.695526330669064</v>
+        <v>-7.771039095157366</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03959498367336423</v>
+        <v>-0.06980008946868521</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.622591647304978</v>
+        <v>-1.681291288156504</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.065416984525022</v>
+        <v>2.030197200014106</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.714261232787661</v>
+        <v>-7.789773997275963</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.001455397356282973</v>
+        <v>-0.02874970843903757</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.622591647304978</v>
+        <v>-1.681291288156504</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.113961326402109</v>
+        <v>2.078741541891193</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.566321191380061</v>
+        <v>-7.641833955868363</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05924750876884488</v>
+        <v>-0.08945261456416542</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.60227073139642</v>
+        <v>-1.660970372247946</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.006274953259076</v>
+        <v>1.97105516874816</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.549163041248767</v>
+        <v>-7.624675805737069</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06109823496980527</v>
+        <v>-0.09130334076512581</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.585112581265126</v>
+        <v>-1.643812222116652</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.007855857084374</v>
+        <v>1.972636072573458</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.505614634478077</v>
+        <v>-7.581127398966379</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05063948435662224</v>
+        <v>-0.08084459015194279</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.585112581265126</v>
+        <v>-1.643812222116652</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.000895244989281</v>
+        <v>1.965675460478365</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.263466241024219</v>
+        <v>-7.33897900551252</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0606822274060641</v>
+        <v>0.03047712161074356</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.585112581265126</v>
+        <v>-1.643812222116652</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.015357599370424</v>
+        <v>1.980137814859508</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.155207103901697</v>
+        <v>-7.230719868389999</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0985180027142678</v>
+        <v>0.06831289691894726</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.585112581265126</v>
+        <v>-1.643812222116652</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.009889719829619</v>
+        <v>1.974669935318703</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.031915969084566</v>
+        <v>-7.107428733572868</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1453325506516969</v>
+        <v>0.1151274448563764</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.461821446447995</v>
+        <v>-1.520521087299521</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.081362494730474</v>
+        <v>2.046142710219558</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.010766770181123</v>
+        <v>-7.086279534669425</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1614932084503997</v>
+        <v>0.1312881026550787</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.440672247544552</v>
+        <v>-1.499371888396078</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.101752992309865</v>
+        <v>2.066533207798949</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.767001328197678</v>
+        <v>-6.84251409268598</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2547800935908282</v>
+        <v>0.2245749877955072</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.440672247544552</v>
+        <v>-1.499371888396078</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.097533700656916</v>
+        <v>2.062313916146</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.620104300479808</v>
+        <v>-6.695617064968109</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3156632185979924</v>
+        <v>0.2854581128026714</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.393014005565964</v>
+        <v>-1.45171364641749</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.128252959764085</v>
+        <v>2.093033175253169</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.370253906530733</v>
+        <v>-6.445766671019035</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4083454511613245</v>
+        <v>0.3781403453660035</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.393014005565964</v>
+        <v>-1.45171364641749</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.120995034747787</v>
+        <v>2.085775250236871</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.194361814063301</v>
+        <v>-6.269874578551603</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4823014116689457</v>
+        <v>0.4520963058736251</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.393014005565964</v>
+        <v>-1.45171364641749</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.124594158268436</v>
+        <v>2.08937437375752</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.022915351040838</v>
+        <v>-6.098428115529139</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5642075029324851</v>
+        <v>0.5340023971371641</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.221567542543501</v>
+        <v>-1.280267183395027</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.240789542136467</v>
+        <v>2.205569757625551</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.797882351372015</v>
+        <v>-5.873395115860316</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6532411804163112</v>
+        <v>0.6230360746209906</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9965345428746778</v>
+        <v>-1.055234183726204</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.374829819554058</v>
+        <v>2.339610035043142</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.73424660913808</v>
+        <v>-5.809759373626382</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6833902783642021</v>
+        <v>0.6531851725688815</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9328988006407433</v>
+        <v>-0.9915984414922695</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.417706065948736</v>
+        <v>2.38248628143782</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.641246567932182</v>
+        <v>-5.716759332420484</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7017845536303571</v>
+        <v>0.6715794478350365</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9328988006407433</v>
+        <v>-0.9915984414922695</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.398900324732532</v>
+        <v>2.363680540221616</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.400816071127322</v>
+        <v>-5.476328835615623</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7996998289771788</v>
+        <v>0.7694947231818579</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.692468303835883</v>
+        <v>-0.7511679446874092</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.544901699440325</v>
+        <v>2.509681914929409</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.328573502956127</v>
+        <v>-5.404086267444429</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8325261700804769</v>
+        <v>0.8023210642851559</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.692468303835883</v>
+        <v>-0.7511679446874092</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.548831013275145</v>
+        <v>2.513611228764229</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.275575180674739</v>
+        <v>-5.351087945163041</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8544040829103721</v>
+        <v>0.8241989771150511</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6371320448339441</v>
+        <v>-0.6958316856854704</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.582711352593649</v>
+        <v>2.547491568082733</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.166770295195012</v>
+        <v>-5.242283059683314</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8949241083222561</v>
+        <v>0.8647190025269356</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6371320448339441</v>
+        <v>-0.6958316856854704</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.579709423813642</v>
+        <v>2.544489639302726</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.946749497158001</v>
+        <v>-5.022262261646303</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9845114645476745</v>
+        <v>0.9543063587523539</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4959121997659639</v>
+        <v>-0.5546118406174901</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.666020367865044</v>
+        <v>2.630800583354129</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.813881808094724</v>
+        <v>-4.889394572583026</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.053552722974809</v>
+        <v>1.023347617179488</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4959121997659639</v>
+        <v>-0.5546118406174901</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.681914550666868</v>
+        <v>2.646694766155952</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.654366704575354</v>
+        <v>-4.729879469063656</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.118504608822859</v>
+        <v>1.088299503027538</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.336397096246594</v>
+        <v>-0.3950967370981202</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.778769457218791</v>
+        <v>2.743549672707876</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.509694559475617</v>
+        <v>-4.585207323963918</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.186461569424194</v>
+        <v>1.156256463628873</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1917249511468566</v>
+        <v>-0.2504245919983828</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.875660846840074</v>
+        <v>2.840441062329158</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.569569386833309</v>
+        <v>-4.645082151321611</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.148549129882543</v>
+        <v>1.118344024087222</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2515997785045487</v>
+        <v>-0.3102994193560749</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.825773441826884</v>
+        <v>2.790553657315969</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.118425199146975</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.598042673172121</v>
+        <v>-4.558282653542602</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.278851705564379</v>
+        <v>1.175464316521392</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2515997785045487</v>
+        <v>-0.3102994193560749</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.967465332044246</v>
+        <v>2.812954150638535</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.118497600520387</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.600512379633927</v>
+        <v>-4.560752360004408</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.277936224353069</v>
+        <v>1.174548835310081</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2540694849663548</v>
+        <v>-0.3127691258178811</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.966055909540575</v>
+        <v>2.811544728134863</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.129504522995089</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.668882565957937</v>
+        <v>-4.629122546328418</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.261595072298167</v>
+        <v>1.158207683255179</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2447937859301399</v>
+        <v>-0.3034934267816661</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.982628251437005</v>
+        <v>2.828117070031294</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.119941231626981</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.777420746874071</v>
+        <v>-4.737660727244552</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.208616508563605</v>
+        <v>1.105229119520617</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2447937859301399</v>
+        <v>-0.3034934267816661</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.973064960068897</v>
+        <v>2.818553778663186</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.944650796667367</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.808413906202777</v>
+        <v>-4.768653886573257</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.02092880987251</v>
+        <v>0.9175414208295216</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2447937859301399</v>
+        <v>-0.3034934267816661</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.797774525109284</v>
+        <v>2.643263343703572</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.949218028659155</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.632939646410307</v>
+        <v>-4.593179626780788</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.095685745781285</v>
+        <v>0.9922983567382968</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2447937859301399</v>
+        <v>-0.3034934267816661</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.802341757101071</v>
+        <v>2.64783057569536</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.924960057420362</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.743875899051556</v>
+        <v>-4.704115879422037</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.027053273485993</v>
+        <v>0.9236658844430043</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2447937859301399</v>
+        <v>-0.3034934267816661</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.778083785862278</v>
+        <v>2.623572604456567</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.928091442640268</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.946902476594789</v>
+        <v>-4.90714245696527</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9489740276886049</v>
+        <v>0.8455866386456166</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4478203634733733</v>
+        <v>-0.5065200043248995</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.659399224556244</v>
+        <v>2.504888043150533</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.9382638290724</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.788976877659496</v>
+        <v>-4.749216858029977</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.022316653694854</v>
+        <v>0.9189292646518661</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4478203634733733</v>
+        <v>-0.5065200043248995</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.669571610988376</v>
+        <v>2.515060429582665</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.93321009964626</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.702733414633118</v>
+        <v>-4.6629733950036</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.051760309479266</v>
+        <v>0.9483729204362776</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4478203634733733</v>
+        <v>-0.5065200043248995</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.664517881562237</v>
+        <v>2.510006700156525</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.924985875090786</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.748040234032098</v>
+        <v>-4.708280214402579</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.025413357164199</v>
+        <v>0.9220259681212113</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4886305264826041</v>
+        <v>-0.5473301673341303</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.631807559201224</v>
+        <v>2.477296377795512</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.925537748123888</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.777073338734399</v>
+        <v>-4.737313319104881</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.014351988316381</v>
+        <v>0.9109645992733924</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4886305264826041</v>
+        <v>-0.5473301673341303</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.632359432234325</v>
+        <v>2.477848250828614</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.854810440015253</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.68426285728354</v>
+        <v>-4.644502837654021</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.98074887278809</v>
+        <v>0.8773614837451018</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3958200450317447</v>
+        <v>-0.454519685883271</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.617318412996207</v>
+        <v>2.462807231590495</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.856683915939854</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.728652326612967</v>
+        <v>-4.688892306983448</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9648665609809199</v>
+        <v>0.8614791719379316</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4402095143611724</v>
+        <v>-0.4989091552126986</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.592558207323151</v>
+        <v>2.438047025917439</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.851759624451577</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.615981108376717</v>
+        <v>-4.576221088747198</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.005010756787143</v>
+        <v>0.9016233677441547</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3275382961249222</v>
+        <v>-0.3862379369764484</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.655236646776624</v>
+        <v>2.500725465370913</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.857250920282244</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.503604107194044</v>
+        <v>-4.463844087564525</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.055452853090879</v>
+        <v>0.9520654640478912</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3275382961249222</v>
+        <v>-0.3862379369764484</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.660727942607291</v>
+        <v>2.50621676120158</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.868748122050783</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.701838676080775</v>
+        <v>-4.662078656451256</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.987656227304726</v>
+        <v>0.8842688382617379</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5257728650116528</v>
+        <v>-0.584472505863179</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.553284403043792</v>
+        <v>2.398773221638081</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.707103842051437</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.784839957106054</v>
+        <v>-4.745079937476535</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7928114348952677</v>
+        <v>0.6894240458522796</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5443437495388266</v>
+        <v>-0.6030433903903527</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.380497592328141</v>
+        <v>2.22598641092243</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.827253502770642</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.911906963413042</v>
+        <v>-4.872146943783523</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8621342930916782</v>
+        <v>0.7587469040486901</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5443437495388266</v>
+        <v>-0.6030433903903527</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.500647253047346</v>
+        <v>2.346136071641635</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.841766528872965</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.998505546394145</v>
+        <v>-4.958745526764626</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8420078860015601</v>
+        <v>0.7386204969585717</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5443437495388266</v>
+        <v>-0.6030433903903527</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.515160279149669</v>
+        <v>2.360649097743958</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.839185970215334</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.960121883835994</v>
+        <v>-4.920361864206475</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8547807923671891</v>
+        <v>0.7513934033242009</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5059600869806754</v>
+        <v>-0.5646597278322015</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.535609918026929</v>
+        <v>2.381098736621218</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.835914999060636</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.783005553800828</v>
+        <v>-4.743245534171309</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9223563532265575</v>
+        <v>0.8189689641835693</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5059600869806754</v>
+        <v>-0.5646597278322015</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.532338946872231</v>
+        <v>2.377827765466519</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.836598390822549</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.753303429824534</v>
+        <v>-4.713543410195015</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.934920594578988</v>
+        <v>0.8315332055359999</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5104302121959887</v>
+        <v>-0.5691298530475148</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.530340263504956</v>
+        <v>2.375829082099245</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.830385366128963</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.573928008585766</v>
+        <v>-4.534167988956248</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.000457738380909</v>
+        <v>0.8970703493379213</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.35365345402527</v>
+        <v>-0.4123530948767962</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.618193293713801</v>
+        <v>2.46368211230809</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.811192821460553</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.618942222106373</v>
+        <v>-4.579182202476854</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9632595083042566</v>
+        <v>0.8598721192612684</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3840023493398746</v>
+        <v>-0.4427019901914008</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.580791411856628</v>
+        <v>2.426280230450917</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.816884383799499</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.885946732378808</v>
+        <v>-4.846186712749289</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8621492665342283</v>
+        <v>0.7587618774912401</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5783653873828232</v>
+        <v>-0.6370650282343493</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.469865151369805</v>
+        <v>2.315353969964094</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.816088305696</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.987144513815981</v>
+        <v>-4.947384494186462</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8208740758558606</v>
+        <v>0.7174866868128724</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6467742009281424</v>
+        <v>-0.7054738417796684</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.428023785139115</v>
+        <v>2.273512603733404</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.813688267250317</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.954668927645208</v>
+        <v>-4.91490890801569</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8314642718784864</v>
+        <v>0.728076882835498</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6467742009281424</v>
+        <v>-0.7054738417796684</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.425623746693432</v>
+        <v>2.27111256528772</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.810212986458562</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.935630799937911</v>
+        <v>-4.895870780308393</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8356042421696501</v>
+        <v>0.732216853126662</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.704957812259337</v>
+        <v>-0.763657453110863</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38723829910296</v>
+        <v>2.232727117697249</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.987794855397242</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.96675743108853</v>
+        <v>-4.926997411459011</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.000735458648083</v>
+        <v>0.8973480696050951</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.704957812259337</v>
+        <v>-0.763657453110863</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.56482016804164</v>
+        <v>2.410308986635929</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.988628184383376</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.019077811689321</v>
+        <v>-4.979317792059803</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9806406353939003</v>
+        <v>0.877253246350912</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6700109522504648</v>
+        <v>-0.7287105931019908</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.586621613033097</v>
+        <v>2.432110431627386</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.994636714780302</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.16340071761424</v>
+        <v>-5.123640697984722</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9289200034208585</v>
+        <v>0.8255326143778703</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6700109522504648</v>
+        <v>-0.7287105931019908</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.592630143430023</v>
+        <v>2.438118962024312</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.073789362572324</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.015657747379238</v>
+        <v>-4.975897727749719</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.067169839306882</v>
+        <v>0.9637824502638932</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5022035950155816</v>
+        <v>-0.5609032358671077</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.772467205562975</v>
+        <v>2.617956024157264</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.076582984103805</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.117672429910459</v>
+        <v>-5.07791241028094</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.029157587825874</v>
+        <v>0.9257701987828857</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5022035950155816</v>
+        <v>-0.5609032358671077</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.775260827094456</v>
+        <v>2.620749645688745</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.077245332495463</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.981063085816366</v>
+        <v>-4.941303066186848</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.084463673855169</v>
+        <v>0.9810762848121812</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3655942509214892</v>
+        <v>-0.4242938917730152</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.85788878194257</v>
+        <v>2.703377600536859</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.076325809235573</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.123828418639016</v>
+        <v>-5.084068399009498</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.02643801746622</v>
+        <v>0.9230506284232312</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5083595837441396</v>
+        <v>-0.5670592245956656</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.77131005898909</v>
+        <v>2.616798877583379</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.142661363032394</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.061530419862894</v>
+        <v>-5.021770400233375</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.117692770773489</v>
+        <v>1.014305381730501</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5083595837441396</v>
+        <v>-0.5670592245956656</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.837645612785911</v>
+        <v>2.683134431380199</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.851242235421792</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.859740222197736</v>
+        <v>-4.819980202568217</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9069897222289507</v>
+        <v>0.8036023331859623</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3103413915749852</v>
+        <v>-0.3690410324265112</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.665037400476801</v>
+        <v>2.51052621907109</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.921532467743968</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.799849540555143</v>
+        <v>-4.760089520925624</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.001236227208163</v>
+        <v>0.8978488381651748</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2504507099323917</v>
+        <v>-0.3091503507839177</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.771262041784533</v>
+        <v>2.616750860378822</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.936160203860011</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.897590085180117</v>
+        <v>-4.857830065550599</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.976767745474217</v>
+        <v>0.8733803564312288</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2663399880653719</v>
+        <v>-0.3250396289168979</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.776356211020788</v>
+        <v>2.621845029615077</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.934696184684683</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.073927845303047</v>
+        <v>-5.034167825673528</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9047686222497169</v>
+        <v>0.8013812332067287</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4426777481883013</v>
+        <v>-0.5013773890398273</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.669089535771702</v>
+        <v>2.514578354365991</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.933187802724611</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.073238473141823</v>
+        <v>-5.033478453512305</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9035359891541348</v>
+        <v>0.8001486001111466</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4426777481883013</v>
+        <v>-0.5013773890398273</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.667581153811631</v>
+        <v>2.51306997240592</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.933050670160048</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.079809438196416</v>
+        <v>-5.040049418566897</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9007704705677337</v>
+        <v>0.7973830815247456</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4492487132428942</v>
+        <v>-0.5079483540944203</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.663501442214312</v>
+        <v>2.5089902608086</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.933050670160048</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.071855467901644</v>
+        <v>-5.032095448272125</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9039520586856429</v>
+        <v>0.8005646696426547</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4492487132428942</v>
+        <v>-0.5079483540944203</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663501442214312</v>
+        <v>2.5089902608086</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.939432427187852</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.061482091568557</v>
+        <v>-5.021722071939038</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9144831662466824</v>
+        <v>0.8110957772036937</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.438875336909807</v>
+        <v>-0.497574977761333</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.676107225041968</v>
+        <v>2.521596043636257</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.944324800562577</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.933797781774261</v>
+        <v>-4.894037762144742</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9704492635391255</v>
+        <v>0.8670618744961374</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3111910271155105</v>
+        <v>-0.3698906679670366</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.757610184293271</v>
+        <v>2.60309900288756</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.931079473038449</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.994464372176649</v>
+        <v>-4.954704352547131</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9329372998540424</v>
+        <v>0.829549910811054</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3928893438340442</v>
+        <v>-0.4515889846855702</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.695345866738023</v>
+        <v>2.540834685332312</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.935177175649078</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.929470512243004</v>
+        <v>-4.889710492613485</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9630325464381291</v>
+        <v>0.8596451573951409</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3660587292298888</v>
+        <v>-0.4247583700814149</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.715541938111145</v>
+        <v>2.561030756705434</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.566240913644361</v>
+        <v>3.724843894270161</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.784485988342569</v>
+        <v>2.696243340900081</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.929470512243004</v>
+        <v>-4.889710492613485</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9630325464381291</v>
+        <v>0.8596451573951409</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3660587292298888</v>
+        <v>-0.4247583700814149</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.777549785328937</v>
+        <v>2.689307137886449</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-62.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-674.8%</t>
+          <t>-681.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.4%</t>
+          <t>458.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.5%</t>
+          <t>-656.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-270.3%</t>
+          <t>-272.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>129.9%</t>
+          <t>-141.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.3%</t>
+          <t>-298.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.0%</t>
+          <t>-148.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-253.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.1%</t>
+          <t>-197.5%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5908024501953608</v>
+        <v>-0.6533643014617114</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.889803315145894</v>
+        <v>2.864778574639353</v>
       </c>
       <c r="F1843" t="n">
         <v>1.455613419548912</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6725743506231125</v>
+        <v>-0.7351362018894632</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.847177280930031</v>
+        <v>2.822152540423491</v>
       </c>
       <c r="F1844" t="n">
         <v>1.482648992955049</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.8023453097613409</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.800034214108442</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-1.009911094152953</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.714832696471038</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.42766511769979</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.545657978557366</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.568392735755242</v>
+        <v>-1.630954587021593</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.489233147934107</v>
+        <v>2.464208407427567</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8954085957821715</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.776396794108319</v>
+        <v>-1.83895864537467</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.410923669146801</v>
+        <v>2.385898928640261</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8954085957821715</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.987809214996294</v>
+        <v>-2.050371066262645</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.3214401571296</v>
+        <v>2.296415416623059</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6839961748941964</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.326967592584817</v>
+        <v>-2.389529443851167</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.17886110540064</v>
+        <v>2.153836364894099</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3448377973056743</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.535458374036501</v>
+        <v>-2.598020225302852</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.115803082558734</v>
+        <v>2.090778342052194</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1363470158539899</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.782659558801723</v>
+        <v>-2.845221410068073</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.025021359061214</v>
+        <v>1.999996618554674</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1565003693528023</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.27504458682582</v>
+        <v>-3.33760643809217</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.829173739895307</v>
+        <v>1.804148999388767</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3358846586712944</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.660224977755892</v>
+        <v>-3.722786829022243</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.673644122336142</v>
+        <v>1.648619381829602</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3358846586712944</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.003907750982555</v>
+        <v>-4.066469602248906</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.537940136500093</v>
+        <v>1.512915395993553</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4437907106985126</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.210419527869576</v>
+        <v>-4.272981379135927</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.451441484401542</v>
+        <v>1.426416743895002</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6503024875855341</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.466260613648269</v>
+        <v>-4.52882246491462</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.350877976790325</v>
+        <v>1.325853236283784</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6503024875855341</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.898066406798057</v>
+        <v>-4.960628258064407</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.164488546997814</v>
+        <v>1.139463806491274</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7867199840268011</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.132760400930609</v>
+        <v>-5.195322252196959</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.058895724346884</v>
+        <v>1.033870983840344</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.7803837167975459</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.468423048161061</v>
+        <v>-5.530984899427412</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9232112571106676</v>
+        <v>0.8981865166041278</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.7803837167975459</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.832049293061375</v>
+        <v>-5.894611144327725</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7842483193847842</v>
+        <v>0.759223578878244</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.8786053536646717</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.197176675700121</v>
+        <v>-6.259738526966472</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6374518813351169</v>
+        <v>0.6124271408285766</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.174916137963684</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.605765452880799</v>
+        <v>-6.66832730414715</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4727779144776045</v>
+        <v>0.4477531739710643</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.583504915144363</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.882341553196632</v>
+        <v>-6.944903404462982</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.357332906822732</v>
+        <v>0.3323081663161922</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.583504915144363</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.298733427483629</v>
+        <v>-7.36129527874998</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1887702077168107</v>
+        <v>0.1637454672102705</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.583504915144363</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.615345370024277</v>
+        <v>-7.677907221290628</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07238412136923023</v>
+        <v>0.04735938086268998</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.583504915144363</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.961220192009087</v>
+        <v>-8.023782043275437</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0698662422789984</v>
+        <v>-0.0948909827855382</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.583504915144363</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.124800070193471</v>
+        <v>-8.187361921459821</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1368932734977508</v>
+        <v>-0.1619180140042911</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.583504915144363</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.421461412003669</v>
+        <v>-8.48402326327002</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2517788342926219</v>
+        <v>-0.2768035747991622</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.652248050878241</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.626492592777986</v>
+        <v>-8.689054444044336</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3378176111367517</v>
+        <v>-0.3628423516432919</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.652248050878241</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.009493981520617</v>
+        <v>-9.072055832786967</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4911202679553881</v>
+        <v>-0.5161450084619283</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.652248050878241</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.191363772505651</v>
+        <v>-9.253925623772002</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5612966683779721</v>
+        <v>-0.5863214088845123</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.834117841863276</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.550894095009653</v>
+        <v>-9.613455946276003</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6997584940815225</v>
+        <v>-0.7247832345880627</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.834117841863276</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.601243158463875</v>
+        <v>-9.663805009730225</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.711982099506034</v>
+        <v>-0.7370068400125738</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.884466905317498</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.698862435885271</v>
+        <v>-9.761424287151621</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7479880598528235</v>
+        <v>-0.7730128003593637</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.982086182738895</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.846388523890914</v>
+        <v>-9.908950375157264</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8041049387335084</v>
+        <v>-0.8291296792400487</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.129612270744539</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.05064669922078</v>
+        <v>-10.11320855048713</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8802950117468118</v>
+        <v>-0.9053197522533516</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.257251215358528</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.19245647342757</v>
+        <v>-10.25501832469392</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9325363669450906</v>
+        <v>-0.9575611074516304</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.428530013004103</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.11898664176012</v>
+        <v>-10.18154849302647</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8877767327846895</v>
+        <v>-0.9128014732912302</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.355060181336655</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.29411105914666</v>
+        <v>-10.35667291041301</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9432712789917908</v>
+        <v>-0.9682960194983306</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.530184598723198</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.52856315316115</v>
+        <v>-10.5911250044275</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.044271281499182</v>
+        <v>-1.069296022005723</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.530184598723198</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.81636699769839</v>
+        <v>-10.87892884896474</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.166065010088054</v>
+        <v>-1.191089750594594</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.817988443260437</v>
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.94466591778702</v>
+        <v>-10.93171500456507</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.21626878828495</v>
+        <v>-1.211088422996168</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.97236357069436</v>
+        <v>-2.913663929842834</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.378535860726989</v>
+        <v>1.413755645237905</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17669483752328</v>
+        <v>-11.16374392430133</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.30638662755034</v>
+        <v>-1.301206262261558</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.034376267882783</v>
+        <v>-2.975676627031257</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.34402197104305</v>
+        <v>1.379241755553966</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12467932355447</v>
+        <v>-11.11172841033251</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.281590086276414</v>
+        <v>-1.276409720987632</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.034376267882783</v>
+        <v>-2.975676627031257</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.348012306729451</v>
+        <v>1.383232091240367</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26635116527859</v>
+        <v>-11.25340025205663</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.339734049864804</v>
+        <v>-1.334553684576022</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.034376267882783</v>
+        <v>-2.975676627031257</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.346537079830709</v>
+        <v>1.381756864341625</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21676032085375</v>
+        <v>-11.2038094076318</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.304844301929997</v>
+        <v>-1.299663936641216</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.98478542345795</v>
+        <v>-2.926085782606423</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.391344996650482</v>
+        <v>1.426564781161398</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.01760821361665</v>
+        <v>-11.0046573003947</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.238234592681841</v>
+        <v>-1.23305422739306</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.819462897508136</v>
+        <v>-2.76076325665661</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.477487378573687</v>
+        <v>1.512707163084603</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.79176306089724</v>
+        <v>-10.77881214767529</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.138317458557867</v>
+        <v>-1.133137093269086</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777536221920973</v>
+        <v>-2.718836581069446</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.512222456962194</v>
+        <v>1.547442241473109</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.66718440455965</v>
+        <v>-10.6542334913377</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.087346851466771</v>
+        <v>-1.082166486177991</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777536221920973</v>
+        <v>-2.718836581069446</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.513361601518252</v>
+        <v>1.548581386029168</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.72007969260394</v>
+        <v>-10.70712877938198</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.105871192522379</v>
+        <v>-1.100690827233597</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.772580875832527</v>
+        <v>-2.713881234981</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.518968583333428</v>
+        <v>1.554188367844344</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.43617096167519</v>
+        <v>-10.42322004845323</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9865739959122424</v>
+        <v>-0.9813936306234616</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.772580875832527</v>
+        <v>-2.713881234981</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.524702287572064</v>
+        <v>1.55992207208298</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.36480456906554</v>
+        <v>-10.35185365584359</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.967764701262249</v>
+        <v>-0.9625843359734674</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.701214483222878</v>
+        <v>-2.642514842371352</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.557784860743988</v>
+        <v>1.593004645254904</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.10096770186147</v>
+        <v>-10.08801678863952</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8721134356935285</v>
+        <v>-0.8669330704047478</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.701214483222878</v>
+        <v>-2.642514842371352</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.54790137943108</v>
+        <v>1.583121163941996</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.833725900993073</v>
+        <v>-9.82077498777112</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7670512758455432</v>
+        <v>-0.761870910556762</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.701214483222878</v>
+        <v>-2.642514842371352</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.546066818931707</v>
+        <v>1.581286603442623</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.735818862316583</v>
+        <v>-9.722867949094629</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.728188775348408</v>
+        <v>-0.7230084100596268</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.633228733362322</v>
+        <v>-2.574529092510796</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.58655795387458</v>
+        <v>1.621777738385495</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.711865321340625</v>
+        <v>-9.698914408118672</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.717938852812531</v>
+        <v>-0.7127584875237498</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.609275192386364</v>
+        <v>-2.550575551534838</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.601598584605648</v>
+        <v>1.636818369116564</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.447805383017828</v>
+        <v>-9.434854469795875</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6255751936451643</v>
+        <v>-0.6203948283563832</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.345215254063568</v>
+        <v>-2.286515613212042</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.746774231437573</v>
+        <v>1.781994015948489</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.740725759512991</v>
+        <v>-8.727774846291037</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3455303779035304</v>
+        <v>-0.3403500126147492</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.345215254063568</v>
+        <v>-2.286515613212042</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.743987197777272</v>
+        <v>1.779206982288188</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.7005414611468</v>
+        <v>-8.687590547924847</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3291130346692128</v>
+        <v>-0.3239326693804316</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.305030955697378</v>
+        <v>-2.246331314845851</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.768441400684828</v>
+        <v>1.803661185195744</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.620471665608996</v>
+        <v>-8.607520752387043</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2977182952333344</v>
+        <v>-0.2925379299445527</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.224961160159574</v>
+        <v>-2.166261519308047</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.815850099228268</v>
+        <v>1.851069883739183</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.386990443379396</v>
+        <v>-8.374039530157443</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1964013775036419</v>
+        <v>-0.1912210122148608</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.991479937929975</v>
+        <v>-1.932780297078449</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.963863261403879</v>
+        <v>1.999083045914795</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.237324052371882</v>
+        <v>-8.224373139149929</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1394270314135957</v>
+        <v>-0.1342466661248141</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.898576446687439</v>
+        <v>-1.839876805835913</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.016713145836442</v>
+        <v>2.051932930347357</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.105048578740995</v>
+        <v>-8.092097665519042</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.09114935521421375</v>
+        <v>-0.08596898992543212</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.766300973056552</v>
+        <v>-1.707601332205026</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.091445916762001</v>
+        <v>2.126665701272916</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.914448904067842</v>
+        <v>-7.901497990845889</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.01209442465731581</v>
+        <v>-0.00691405936853462</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.5757012983834</v>
+        <v>-1.517001657531873</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.208620782253529</v>
+        <v>2.243840566764445</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.665449105384261</v>
+        <v>-7.794828196730697</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1004118360397754</v>
+        <v>0.04866019950120082</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.5757012983834</v>
+        <v>-1.517001657531873</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.221527123477188</v>
+        <v>2.256746907988104</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.771039095157366</v>
+        <v>-7.900418186503802</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06980008946868521</v>
+        <v>-0.1215517260072598</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.681291288156504</v>
+        <v>-1.622591647304978</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.030197200014106</v>
+        <v>2.065416984525022</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.789773997275963</v>
+        <v>-7.919153088622399</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02874970843903757</v>
+        <v>-0.08050134497761219</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.681291288156504</v>
+        <v>-1.622591647304978</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.078741541891193</v>
+        <v>2.113961326402109</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.641833955868363</v>
+        <v>-7.7712130472148</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08945261456416542</v>
+        <v>-0.14120425110274</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.660970372247946</v>
+        <v>-1.60227073139642</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.97105516874816</v>
+        <v>2.006274953259076</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.624675805737069</v>
+        <v>-7.754054897083505</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09130334076512581</v>
+        <v>-0.1430549773037004</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.643812222116652</v>
+        <v>-1.585112581265126</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.972636072573458</v>
+        <v>2.007855857084374</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.581127398966379</v>
+        <v>-7.710506490312815</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08084459015194279</v>
+        <v>-0.1325962266905174</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.643812222116652</v>
+        <v>-1.585112581265126</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.965675460478365</v>
+        <v>2.000895244989281</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.33897900551252</v>
+        <v>-7.468358096858957</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03047712161074356</v>
+        <v>-0.02127451492783106</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.643812222116652</v>
+        <v>-1.585112581265126</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.980137814859508</v>
+        <v>2.015357599370424</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.230719868389999</v>
+        <v>-7.360098959736435</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06831289691894726</v>
+        <v>0.01656126038037264</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.643812222116652</v>
+        <v>-1.585112581265126</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.974669935318703</v>
+        <v>2.009889719829619</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.107428733572868</v>
+        <v>-7.236807824919304</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1151274448563764</v>
+        <v>0.06337580831780176</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.520521087299521</v>
+        <v>-1.461821446447995</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.046142710219558</v>
+        <v>2.081362494730474</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.086279534669425</v>
+        <v>-7.145176007943546</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1312881026550787</v>
+        <v>0.1077295133454306</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.499371888396078</v>
+        <v>-1.370189629472237</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.066533207798949</v>
+        <v>2.144042563153254</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.84251409268598</v>
+        <v>-6.901410565960101</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2245749877955072</v>
+        <v>0.2010163984858591</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.499371888396078</v>
+        <v>-1.370189629472237</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.062313916146</v>
+        <v>2.139823271500305</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.695617064968109</v>
+        <v>-6.754513538242231</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2854581128026714</v>
+        <v>0.2618995234930233</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.45171364641749</v>
+        <v>-1.322531387493649</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.093033175253169</v>
+        <v>2.170542530607474</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.445766671019035</v>
+        <v>-6.504663144293156</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3781403453660035</v>
+        <v>0.3545817560563553</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.45171364641749</v>
+        <v>-1.322531387493649</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.085775250236871</v>
+        <v>2.163284605591176</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.269874578551603</v>
+        <v>-6.328771051825724</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4520963058736251</v>
+        <v>0.4285377165639765</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.45171364641749</v>
+        <v>-1.322531387493649</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.08937437375752</v>
+        <v>2.166883729111825</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.098428115529139</v>
+        <v>-6.15732458880326</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5340023971371641</v>
+        <v>0.510443807827516</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.280267183395027</v>
+        <v>-1.151084924471186</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.205569757625551</v>
+        <v>2.283079112979856</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.873395115860316</v>
+        <v>-5.932291589134437</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6230360746209906</v>
+        <v>0.599477485311342</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.055234183726204</v>
+        <v>-0.926051924802363</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.339610035043142</v>
+        <v>2.417119390397447</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.809759373626382</v>
+        <v>-5.868655846900503</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6531851725688815</v>
+        <v>0.6296265832592329</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9915984414922695</v>
+        <v>-0.8624161825684284</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.38248628143782</v>
+        <v>2.459995636792125</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.716759332420484</v>
+        <v>-5.775655805694605</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6715794478350365</v>
+        <v>0.6480208585253879</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9915984414922695</v>
+        <v>-0.8624161825684284</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.363680540221616</v>
+        <v>2.441189895575921</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.476328835615623</v>
+        <v>-5.535225308889745</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7694947231818579</v>
+        <v>0.7459361338722097</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7511679446874092</v>
+        <v>-0.6219856857635682</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.509681914929409</v>
+        <v>2.587191270283714</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.404086267444429</v>
+        <v>-5.46298274071855</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8023210642851559</v>
+        <v>0.7787624749755078</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7511679446874092</v>
+        <v>-0.6219856857635682</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.513611228764229</v>
+        <v>2.591120584118534</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.351087945163041</v>
+        <v>-5.409984418437162</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8241989771150511</v>
+        <v>0.8006403878054029</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6958316856854704</v>
+        <v>-0.5666494267616293</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.547491568082733</v>
+        <v>2.625000923437038</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.242283059683314</v>
+        <v>-5.301179532957435</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8647190025269356</v>
+        <v>0.841160413217287</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6958316856854704</v>
+        <v>-0.5666494267616293</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.544489639302726</v>
+        <v>2.621998994657031</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.022262261646303</v>
+        <v>-5.081158734920424</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9543063587523539</v>
+        <v>0.9307477694427053</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5546118406174901</v>
+        <v>-0.4254295816936491</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.630800583354129</v>
+        <v>2.708309938708433</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.889394572583026</v>
+        <v>-4.948291045857147</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.023347617179488</v>
+        <v>0.9997890278698398</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5546118406174901</v>
+        <v>-0.4254295816936491</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.646694766155952</v>
+        <v>2.724204121510256</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.729879469063656</v>
+        <v>-4.788775942337777</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.088299503027538</v>
+        <v>1.06474091371789</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3950967370981202</v>
+        <v>-0.2659144781742792</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.743549672707876</v>
+        <v>2.821059028062181</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.585207323963918</v>
+        <v>-4.644103797238039</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.156256463628873</v>
+        <v>1.132697874319224</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2504245919983828</v>
+        <v>-0.1212423330745417</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.840441062329158</v>
+        <v>2.917950417683463</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.645082151321611</v>
+        <v>-4.703978624595732</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.118344024087222</v>
+        <v>1.094785434777573</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3102994193560749</v>
+        <v>-0.1811171604322339</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.790553657315969</v>
+        <v>2.868063012670273</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.558282653542602</v>
+        <v>-4.617179126816723</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.175464316521392</v>
+        <v>1.151905727211743</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3102994193560749</v>
+        <v>-0.1811171604322339</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.812954150638535</v>
+        <v>2.890463505992839</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.560752360004408</v>
+        <v>-4.619648833278529</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.174548835310081</v>
+        <v>1.150990246000433</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3127691258178811</v>
+        <v>-0.18358686689404</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.811544728134863</v>
+        <v>2.889054083489168</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.629122546328418</v>
+        <v>-4.688019019602539</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.158207683255179</v>
+        <v>1.134649093945531</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3034934267816661</v>
+        <v>-0.1743111678578251</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.828117070031294</v>
+        <v>2.905626425385599</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.737660727244552</v>
+        <v>-4.796557200518673</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.105229119520617</v>
+        <v>1.081670530210968</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3034934267816661</v>
+        <v>-0.1743111678578251</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.818553778663186</v>
+        <v>2.89606313401749</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.768653886573257</v>
+        <v>-4.827550359847378</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9175414208295216</v>
+        <v>0.8939828315198732</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3034934267816661</v>
+        <v>-0.1743111678578251</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.643263343703572</v>
+        <v>2.720772699057877</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.593179626780788</v>
+        <v>-4.652076100054909</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9922983567382968</v>
+        <v>0.9687397674286484</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3034934267816661</v>
+        <v>-0.1743111678578251</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.64783057569536</v>
+        <v>2.725339931049665</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.704115879422037</v>
+        <v>-4.763012352696158</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9236658844430043</v>
+        <v>0.900107295133356</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3034934267816661</v>
+        <v>-0.1743111678578251</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.623572604456567</v>
+        <v>2.701081959810872</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.90714245696527</v>
+        <v>-4.966038930239391</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8455866386456166</v>
+        <v>0.8220280493359682</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5065200043248995</v>
+        <v>-0.3773377454010585</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.504888043150533</v>
+        <v>2.582397398504837</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.749216858029977</v>
+        <v>-4.808113331304098</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9189292646518661</v>
+        <v>0.8953706753422177</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5065200043248995</v>
+        <v>-0.3773377454010585</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.515060429582665</v>
+        <v>2.59256978493697</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.6629733950036</v>
+        <v>-4.721869868277721</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9483729204362776</v>
+        <v>0.9248143311266293</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5065200043248995</v>
+        <v>-0.3773377454010585</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.510006700156525</v>
+        <v>2.58751605551083</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.708280214402579</v>
+        <v>-4.767176687676701</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9220259681212113</v>
+        <v>0.8984673788115627</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5473301673341303</v>
+        <v>-0.4181479084102893</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.477296377795512</v>
+        <v>2.554805733149817</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.737313319104881</v>
+        <v>-4.796209792379002</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9109645992733924</v>
+        <v>0.887406009963744</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5473301673341303</v>
+        <v>-0.4181479084102893</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.477848250828614</v>
+        <v>2.555357606182918</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.644502837654021</v>
+        <v>-4.703399310928142</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8773614837451018</v>
+        <v>0.8538028944354534</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.454519685883271</v>
+        <v>-0.3253374269594299</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.462807231590495</v>
+        <v>2.5403165869448</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.688892306983448</v>
+        <v>-4.74778878025757</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8614791719379316</v>
+        <v>0.8379205826282832</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4989091552126986</v>
+        <v>-0.3697268962888576</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.438047025917439</v>
+        <v>2.515556381271744</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.576221088747198</v>
+        <v>-4.635117562021319</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9016233677441547</v>
+        <v>0.8780647784345064</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3862379369764484</v>
+        <v>-0.2570556780526074</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.500725465370913</v>
+        <v>2.578234820725217</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.463844087564525</v>
+        <v>-4.522740560838646</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9520654640478912</v>
+        <v>0.9285068747382428</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3862379369764484</v>
+        <v>-0.2570556780526074</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.50621676120158</v>
+        <v>2.583726116555884</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.662078656451256</v>
+        <v>-4.720975129725377</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8842688382617379</v>
+        <v>0.8607102489520895</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.584472505863179</v>
+        <v>-0.455290246939338</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.398773221638081</v>
+        <v>2.476282576992385</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.745079937476535</v>
+        <v>-4.803976410750656</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6894240458522796</v>
+        <v>0.6658654565426312</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6030433903903527</v>
+        <v>-0.4738611314665117</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.22598641092243</v>
+        <v>2.303495766276734</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.872146943783523</v>
+        <v>-4.931043417057644</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7587469040486901</v>
+        <v>0.7351883147390414</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6030433903903527</v>
+        <v>-0.4738611314665117</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.346136071641635</v>
+        <v>2.42364542699594</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.958745526764626</v>
+        <v>-5.017642000038747</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7386204969585717</v>
+        <v>0.7150619076489235</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6030433903903527</v>
+        <v>-0.4738611314665117</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.360649097743958</v>
+        <v>2.438158453098263</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.920361864206475</v>
+        <v>-4.979258337480596</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7513934033242009</v>
+        <v>0.7278348140145525</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5646597278322015</v>
+        <v>-0.4354774689083605</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.381098736621218</v>
+        <v>2.458608091975522</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.743245534171309</v>
+        <v>-4.80214200744543</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8189689641835693</v>
+        <v>0.7954103748739207</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5646597278322015</v>
+        <v>-0.4354774689083605</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.377827765466519</v>
+        <v>2.455337120820824</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.713543410195015</v>
+        <v>-4.772439883469136</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8315332055359999</v>
+        <v>0.8079746162263515</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5691298530475148</v>
+        <v>-0.4399475941236739</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.375829082099245</v>
+        <v>2.453338437453549</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.534167988956248</v>
+        <v>-4.593064462230369</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8970703493379213</v>
+        <v>0.8735117600282729</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4123530948767962</v>
+        <v>-0.2831708359529552</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.46368211230809</v>
+        <v>2.541191467662395</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.579182202476854</v>
+        <v>-4.638078675750975</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8598721192612684</v>
+        <v>0.83631352995162</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4427019901914008</v>
+        <v>-0.3135197312675598</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.426280230450917</v>
+        <v>2.503789585805221</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.846186712749289</v>
+        <v>-4.90508318602341</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7587618774912401</v>
+        <v>0.7352032881815918</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6370650282343493</v>
+        <v>-0.5078827693105084</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.315353969964094</v>
+        <v>2.392863325318398</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.947384494186462</v>
+        <v>-5.006280967460583</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7174866868128724</v>
+        <v>0.693928097503224</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7054738417796684</v>
+        <v>-0.5762915828558275</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.273512603733404</v>
+        <v>2.351021959087708</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.91490890801569</v>
+        <v>-4.973805381289811</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.728076882835498</v>
+        <v>0.7045182935258496</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7054738417796684</v>
+        <v>-0.5762915828558275</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.27111256528772</v>
+        <v>2.348621920642025</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.895870780308393</v>
+        <v>-4.954767253582514</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.732216853126662</v>
+        <v>0.7086582638170134</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.763657453110863</v>
+        <v>-0.634475194187022</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.232727117697249</v>
+        <v>2.310236473051553</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.810953543768579</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.926997411459011</v>
+        <v>-4.985893884733132</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8973480696050951</v>
+        <v>0.8162395655615791</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.763657453110863</v>
+        <v>-0.634475194187022</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.410308986635929</v>
+        <v>2.430268427256366</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.811786872754713</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.979317792059803</v>
+        <v>-5.038214265333924</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.877253246350912</v>
+        <v>0.796144742307396</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7287105931019908</v>
+        <v>-0.5995283341781499</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.432110431627386</v>
+        <v>2.452069872247823</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.817795403151639</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.123640697984722</v>
+        <v>-5.182537171258843</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8255326143778703</v>
+        <v>0.7444241103343541</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7287105931019908</v>
+        <v>-0.5995283341781499</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.438118962024312</v>
+        <v>2.458078402644749</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.89694805094366</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.975897727749719</v>
+        <v>-5.03479420102384</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9637824502638932</v>
+        <v>0.8826739462203772</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5609032358671077</v>
+        <v>-0.4317209769432667</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.617956024157264</v>
+        <v>2.637915464777701</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.899741672475141</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.07791241028094</v>
+        <v>-5.136808883555061</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9257701987828857</v>
+        <v>0.8446616947393695</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5609032358671077</v>
+        <v>-0.4317209769432667</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.620749645688745</v>
+        <v>2.640709086309182</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.9004040208668</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.941303066186848</v>
+        <v>-5.000199539460969</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9810762848121812</v>
+        <v>0.899967780768665</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4242938917730152</v>
+        <v>-0.2951116328491742</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.703377600536859</v>
+        <v>2.723337041157296</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.89948449760691</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.084068399009498</v>
+        <v>-5.142964872283619</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9230506284232312</v>
+        <v>0.8419421243797154</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5670592245956656</v>
+        <v>-0.4378769656718247</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.616798877583379</v>
+        <v>2.636758318203816</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.965820051403731</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.021770400233375</v>
+        <v>-5.080666873507496</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.014305381730501</v>
+        <v>0.933196877686985</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5670592245956656</v>
+        <v>-0.4378769656718247</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.683134431380199</v>
+        <v>2.703093872000637</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.674400923793129</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.819980202568217</v>
+        <v>-4.878876675842339</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8036023331859623</v>
+        <v>0.7224938291424463</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3690410324265112</v>
+        <v>-0.2398587735026703</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.51052621907109</v>
+        <v>2.530485659691527</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.744691156115304</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.760089520925624</v>
+        <v>-4.818985994199745</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8978488381651748</v>
+        <v>0.8167403341216588</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3091503507839177</v>
+        <v>-0.1799680918600768</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.616750860378822</v>
+        <v>2.636710300999258</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.759318892231348</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.857830065550599</v>
+        <v>-4.91672653882472</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8733803564312288</v>
+        <v>0.7922718523877128</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3250396289168979</v>
+        <v>-0.195857369993057</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.621845029615077</v>
+        <v>2.641804470235514</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.75785487305602</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.034167825673528</v>
+        <v>-5.093064298947649</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8013812332067287</v>
+        <v>0.7202727291632125</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5013773890398273</v>
+        <v>-0.3721951301159864</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.514578354365991</v>
+        <v>2.534537794986428</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.756346491095948</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.033478453512305</v>
+        <v>-5.092374926786426</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8001486001111466</v>
+        <v>0.7190400960676304</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5013773890398273</v>
+        <v>-0.3721951301159864</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.51306997240592</v>
+        <v>2.533029413026357</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.756209358531384</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.040049418566897</v>
+        <v>-5.098945891841018</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7973830815247456</v>
+        <v>0.7162745774812298</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5079483540944203</v>
+        <v>-0.3787660951705793</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.5089902608086</v>
+        <v>2.528949701429037</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.756209358531384</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.032095448272125</v>
+        <v>-5.090991921546246</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8005646696426547</v>
+        <v>0.7194561655991385</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5079483540944203</v>
+        <v>-0.3787660951705793</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.5089902608086</v>
+        <v>2.528949701429037</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.762591115559188</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.021722071939038</v>
+        <v>-5.080618545213159</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8110957772036937</v>
+        <v>0.7299872731601775</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.497574977761333</v>
+        <v>-0.368392718837492</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.521596043636257</v>
+        <v>2.541555484256694</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.767483488933913</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.894037762144742</v>
+        <v>-4.952934235418863</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8670618744961374</v>
+        <v>0.7859533704526207</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3698906679670366</v>
+        <v>-0.2407084090431956</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.60309900288756</v>
+        <v>2.623058443507996</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.754238161409786</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.954704352547131</v>
+        <v>-5.013600825821252</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.829549910811054</v>
+        <v>0.7484414067675376</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4515889846855702</v>
+        <v>-0.3224067257617292</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.540834685332312</v>
+        <v>2.560794125952748</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.758335864020414</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.889710492613485</v>
+        <v>-4.948606965887606</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8596451573951409</v>
+        <v>0.7785366533516243</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4247583700814149</v>
+        <v>-0.2955761111575739</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.561030756705434</v>
+        <v>2.58099019732587</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.724843894270161</v>
+        <v>3.749782124634905</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.696243340900081</v>
+        <v>2.492269262914626</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.889710492613485</v>
+        <v>-4.948606965887606</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8596451573951409</v>
+        <v>0.7785366533516243</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4247583700814149</v>
+        <v>-0.2955761111575739</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.689307137886449</v>
+        <v>2.485333059900994</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-62.4%</t>
+          <t>-29.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.1%</t>
+          <t>-674.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.7%</t>
+          <t>455.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-656.4%</t>
+          <t>-641.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.8%</t>
+          <t>-270.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.4%</t>
+          <t>-286.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.8%</t>
+          <t>-151.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-253.6%</t>
+          <t>-259.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-197.5%</t>
+          <t>-185.5%</t>
         </is>
       </c>
     </row>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.6533643014617114</v>
+        <v>-0.5908024501953608</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.864778574639353</v>
+        <v>2.889803315145894</v>
       </c>
       <c r="F1843" t="n">
         <v>1.455613419548912</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.7351362018894632</v>
+        <v>-0.6725743506231125</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.822152540423491</v>
+        <v>2.847177280930031</v>
       </c>
       <c r="F1844" t="n">
         <v>1.482648992955049</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8023453097613409</v>
+        <v>-0.7397834584949903</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.800034214108442</v>
+        <v>2.825058954614982</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.009911094152953</v>
+        <v>-0.9473492428866022</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.714832696471038</v>
+        <v>2.739857436977578</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.42766511769979</v>
+        <v>-1.365103266433439</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.545657978557366</v>
+        <v>2.570682719063906</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.630954587021593</v>
+        <v>-1.568392735755242</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.464208407427567</v>
+        <v>2.489233147934107</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8954085957821715</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.83895864537467</v>
+        <v>-1.776396794108319</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.385898928640261</v>
+        <v>2.410923669146801</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8954085957821715</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.050371066262645</v>
+        <v>-1.987809214996294</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.296415416623059</v>
+        <v>2.3214401571296</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6839961748941964</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.389529443851167</v>
+        <v>-2.326967592584817</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.153836364894099</v>
+        <v>2.17886110540064</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3448377973056743</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.598020225302852</v>
+        <v>-2.535458374036501</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.090778342052194</v>
+        <v>2.115803082558734</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1363470158539899</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.845221410068073</v>
+        <v>-2.782659558801723</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.999996618554674</v>
+        <v>2.025021359061214</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1565003693528023</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.33760643809217</v>
+        <v>-3.27504458682582</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.804148999388767</v>
+        <v>1.829173739895307</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3358846586712944</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.722786829022243</v>
+        <v>-3.660224977755892</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.648619381829602</v>
+        <v>1.673644122336142</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3358846586712944</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.066469602248906</v>
+        <v>-4.003907750982555</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.512915395993553</v>
+        <v>1.537940136500093</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4437907106985126</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.272981379135927</v>
+        <v>-4.210419527869576</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.426416743895002</v>
+        <v>1.451441484401542</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6503024875855341</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.52882246491462</v>
+        <v>-4.466260613648269</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.325853236283784</v>
+        <v>1.350877976790325</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6503024875855341</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.960628258064407</v>
+        <v>-4.898066406798057</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.139463806491274</v>
+        <v>1.164488546997814</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7867199840268011</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.195322252196959</v>
+        <v>-5.132760400930609</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.033870983840344</v>
+        <v>1.058895724346884</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.7803837167975459</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.530984899427412</v>
+        <v>-5.468423048161061</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8981865166041278</v>
+        <v>0.9232112571106676</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.7803837167975459</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.894611144327725</v>
+        <v>-5.832049293061375</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.759223578878244</v>
+        <v>0.7842483193847842</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.8786053536646717</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.259738526966472</v>
+        <v>-6.197176675700121</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6124271408285766</v>
+        <v>0.6374518813351169</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.174916137963684</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.66832730414715</v>
+        <v>-6.605765452880799</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4477531739710643</v>
+        <v>0.4727779144776045</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.583504915144363</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.944903404462982</v>
+        <v>-6.882341553196632</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3323081663161922</v>
+        <v>0.357332906822732</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.583504915144363</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.36129527874998</v>
+        <v>-7.298733427483629</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1637454672102705</v>
+        <v>0.1887702077168107</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.583504915144363</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.677907221290628</v>
+        <v>-7.615345370024277</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04735938086268998</v>
+        <v>0.07238412136923023</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.583504915144363</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.023782043275437</v>
+        <v>-7.961220192009087</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0948909827855382</v>
+        <v>-0.0698662422789984</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.583504915144363</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.187361921459821</v>
+        <v>-8.124800070193471</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1619180140042911</v>
+        <v>-0.1368932734977508</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.583504915144363</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.48402326327002</v>
+        <v>-8.421461412003669</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2768035747991622</v>
+        <v>-0.2517788342926219</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.652248050878241</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.689054444044336</v>
+        <v>-8.626492592777986</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3628423516432919</v>
+        <v>-0.3378176111367517</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.652248050878241</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.072055832786967</v>
+        <v>-9.009493981520617</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5161450084619283</v>
+        <v>-0.4911202679553881</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.652248050878241</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.253925623772002</v>
+        <v>-9.191363772505651</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5863214088845123</v>
+        <v>-0.5612966683779721</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.834117841863276</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.613455946276003</v>
+        <v>-9.550894095009653</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7247832345880627</v>
+        <v>-0.6997584940815225</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.834117841863276</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.663805009730225</v>
+        <v>-9.601243158463875</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7370068400125738</v>
+        <v>-0.711982099506034</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.884466905317498</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.761424287151621</v>
+        <v>-9.698862435885271</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7730128003593637</v>
+        <v>-0.7479880598528235</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.982086182738895</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.908950375157264</v>
+        <v>-9.846388523890914</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8291296792400487</v>
+        <v>-0.8041049387335084</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.129612270744539</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.11320855048713</v>
+        <v>-10.05064669922078</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9053197522533516</v>
+        <v>-0.8802950117468118</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.257251215358528</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.25501832469392</v>
+        <v>-10.19245647342757</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9575611074516304</v>
+        <v>-0.9325363669450906</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.428530013004103</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.18154849302647</v>
+        <v>-10.11898664176012</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9128014732912302</v>
+        <v>-0.8877767327846895</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.355060181336655</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.35667291041301</v>
+        <v>-10.29411105914666</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9682960194983306</v>
+        <v>-0.9432712789917908</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.530184598723198</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.5911250044275</v>
+        <v>-10.52856315316115</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.069296022005723</v>
+        <v>-1.044271281499182</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.530184598723198</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.87892884896474</v>
+        <v>-10.81636699769839</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.191089750594594</v>
+        <v>-1.166065010088054</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.817988443260437</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.93171500456507</v>
+        <v>-10.86915315329871</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.211088422996168</v>
+        <v>-1.186063682489628</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.913663929842834</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.16374392430133</v>
+        <v>-11.10118207303498</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.301206262261558</v>
+        <v>-1.276181521755019</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.975676627031257</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.11172841033251</v>
+        <v>-11.04916655906616</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.276409720987632</v>
+        <v>-1.251384980481093</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.975676627031257</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.25340025205663</v>
+        <v>-11.19083840079028</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.334553684576022</v>
+        <v>-1.309528944069482</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.975676627031257</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.2038094076318</v>
+        <v>-11.14124755636545</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.299663936641216</v>
+        <v>-1.274639196134676</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.926085782606423</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.0046573003947</v>
+        <v>-10.94209544912835</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.23305422739306</v>
+        <v>-1.20802948688652</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.76076325665661</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.77881214767529</v>
+        <v>-10.71625029640894</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.133137093269086</v>
+        <v>-1.108112352762547</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.718836581069446</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.6542334913377</v>
+        <v>-10.59167164007135</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.082166486177991</v>
+        <v>-1.057141745671451</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.718836581069446</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.70712877938198</v>
+        <v>-10.64456692811564</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.100690827233597</v>
+        <v>-1.075666086727058</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.713881234981</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42322004845323</v>
+        <v>-10.36065819718689</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9813936306234616</v>
+        <v>-0.9563688901169218</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.713881234981</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.35185365584359</v>
+        <v>-10.28929180457724</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9625843359734674</v>
+        <v>-0.9375595954669285</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.642514842371352</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08801678863952</v>
+        <v>-10.02545493737317</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8669330704047478</v>
+        <v>-0.841908329898208</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.642514842371352</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.82077498777112</v>
+        <v>-9.758213136504772</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.761870910556762</v>
+        <v>-0.7368461700502227</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.642514842371352</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.722867949094629</v>
+        <v>-9.660306097828281</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7230084100596268</v>
+        <v>-0.697983669553087</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.574529092510796</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.698914408118672</v>
+        <v>-9.636352556852323</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7127584875237498</v>
+        <v>-0.6877337470172105</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.550575551534838</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.434854469795875</v>
+        <v>-9.372292618529526</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6203948283563832</v>
+        <v>-0.5953700878498438</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.286515613212042</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.727774846291037</v>
+        <v>-8.665212995024689</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3403500126147492</v>
+        <v>-0.3153252721082098</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.286515613212042</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.687590547924847</v>
+        <v>-8.625028696658498</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3239326693804316</v>
+        <v>-0.2989079288738923</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.246331314845851</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.607520752387043</v>
+        <v>-8.544958901120694</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2925379299445527</v>
+        <v>-0.2675131894380134</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.166261519308047</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.374039530157443</v>
+        <v>-8.311477678891094</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1912210122148608</v>
+        <v>-0.1661962717083214</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.932780297078449</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785791</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.224373139149929</v>
+        <v>-8.16181128788358</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1342466661248141</v>
+        <v>-0.1092219256182747</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.839876805835913</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.092097665519042</v>
+        <v>-8.029535814252693</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08596898992543212</v>
+        <v>-0.06094424941889276</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.707601332205026</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.901497990845889</v>
+        <v>-7.83893613957954</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.00691405936853462</v>
+        <v>0.01811068113800474</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.517001657531873</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.794828196730697</v>
+        <v>-7.589936340895959</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.04866019950120082</v>
+        <v>0.130616941835096</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.517001657531873</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.900418186503802</v>
+        <v>-7.695526330669064</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1215517260072598</v>
+        <v>-0.03959498367336423</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.622591647304978</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.919153088622399</v>
+        <v>-7.714261232787661</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.08050134497761219</v>
+        <v>0.001455397356282973</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.622591647304978</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.7712130472148</v>
+        <v>-7.566321191380061</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.14120425110274</v>
+        <v>-0.05924750876884488</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.60227073139642</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.754054897083505</v>
+        <v>-7.549163041248767</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1430549773037004</v>
+        <v>-0.06109823496980527</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.585112581265126</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.710506490312815</v>
+        <v>-7.505614634478077</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1325962266905174</v>
+        <v>-0.05063948435662224</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.585112581265126</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.468358096858957</v>
+        <v>-7.263466241024219</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02127451492783106</v>
+        <v>0.0606822274060641</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.585112581265126</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.360098959736435</v>
+        <v>-7.155207103901697</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.01656126038037264</v>
+        <v>0.0985180027142678</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.585112581265126</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.236807824919304</v>
+        <v>-7.031915969084566</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06337580831780176</v>
+        <v>0.1453325506516969</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.461821446447995</v>
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.145176007943546</v>
+        <v>-7.010766770181123</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1077295133454306</v>
+        <v>0.1614932084503997</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.370189629472237</v>
+        <v>-1.440672247544552</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.144042563153254</v>
+        <v>2.101752992309865</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.901410565960101</v>
+        <v>-6.767001328197678</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2010163984858591</v>
+        <v>0.2547800935908282</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.370189629472237</v>
+        <v>-1.440672247544552</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.139823271500305</v>
+        <v>2.097533700656916</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.754513538242231</v>
+        <v>-6.620104300479808</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2618995234930233</v>
+        <v>0.3156632185979924</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.322531387493649</v>
+        <v>-1.393014005565964</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.170542530607474</v>
+        <v>2.128252959764085</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.504663144293156</v>
+        <v>-6.370253906530733</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3545817560563553</v>
+        <v>0.4083454511613245</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.322531387493649</v>
+        <v>-1.393014005565964</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.163284605591176</v>
+        <v>2.120995034747787</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.328771051825724</v>
+        <v>-6.194361814063301</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4285377165639765</v>
+        <v>0.4823014116689457</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.322531387493649</v>
+        <v>-1.393014005565964</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.166883729111825</v>
+        <v>2.124594158268436</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.15732458880326</v>
+        <v>-6.022915351040838</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.510443807827516</v>
+        <v>0.5642075029324851</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.151084924471186</v>
+        <v>-1.221567542543501</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.283079112979856</v>
+        <v>2.240789542136467</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.932291589134437</v>
+        <v>-5.797882351372015</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.599477485311342</v>
+        <v>0.6532411804163112</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.926051924802363</v>
+        <v>-0.9965345428746778</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.417119390397447</v>
+        <v>2.374829819554058</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.868655846900503</v>
+        <v>-5.73424660913808</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6296265832592329</v>
+        <v>0.6833902783642021</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8624161825684284</v>
+        <v>-0.9328988006407433</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.459995636792125</v>
+        <v>2.417706065948736</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.775655805694605</v>
+        <v>-5.641246567932182</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6480208585253879</v>
+        <v>0.7017845536303571</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8624161825684284</v>
+        <v>-0.9328988006407433</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.441189895575921</v>
+        <v>2.398900324732532</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.535225308889745</v>
+        <v>-5.400816071127322</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7459361338722097</v>
+        <v>0.7996998289771788</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6219856857635682</v>
+        <v>-0.692468303835883</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.587191270283714</v>
+        <v>2.544901699440325</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.46298274071855</v>
+        <v>-5.328573502956127</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7787624749755078</v>
+        <v>0.8325261700804769</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6219856857635682</v>
+        <v>-0.692468303835883</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.591120584118534</v>
+        <v>2.548831013275145</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.409984418437162</v>
+        <v>-5.275575180674739</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8006403878054029</v>
+        <v>0.8544040829103721</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5666494267616293</v>
+        <v>-0.6371320448339441</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.625000923437038</v>
+        <v>2.582711352593649</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.301179532957435</v>
+        <v>-5.166770295195012</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.841160413217287</v>
+        <v>0.8949241083222561</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5666494267616293</v>
+        <v>-0.6371320448339441</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.621998994657031</v>
+        <v>2.579709423813642</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.081158734920424</v>
+        <v>-4.946749497158001</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9307477694427053</v>
+        <v>0.9845114645476745</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4254295816936491</v>
+        <v>-0.4959121997659639</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.708309938708433</v>
+        <v>2.666020367865044</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.948291045857147</v>
+        <v>-4.813881808094724</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9997890278698398</v>
+        <v>1.053552722974809</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4254295816936491</v>
+        <v>-0.4959121997659639</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.724204121510256</v>
+        <v>2.681914550666868</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.788775942337777</v>
+        <v>-4.654366704575354</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.06474091371789</v>
+        <v>1.118504608822859</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2659144781742792</v>
+        <v>-0.336397096246594</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.821059028062181</v>
+        <v>2.778769457218791</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.644103797238039</v>
+        <v>-4.509694559475617</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.132697874319224</v>
+        <v>1.186461569424194</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1212423330745417</v>
+        <v>-0.1917249511468566</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.917950417683463</v>
+        <v>2.875660846840074</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.703978624595732</v>
+        <v>-4.569569386833309</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.094785434777573</v>
+        <v>1.148549129882543</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1811171604322339</v>
+        <v>-0.2515997785045487</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.868063012670273</v>
+        <v>2.825773441826884</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.617179126816723</v>
+        <v>-4.4827698890543</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.151905727211743</v>
+        <v>1.205669422316712</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1811171604322339</v>
+        <v>-0.2515997785045487</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.890463505992839</v>
+        <v>2.84817393514945</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.619648833278529</v>
+        <v>-4.485239595516106</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.150990246000433</v>
+        <v>1.204753941105402</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.18358686689404</v>
+        <v>-0.2540694849663548</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.889054083489168</v>
+        <v>2.846764512645779</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.688019019602539</v>
+        <v>-4.553609781840116</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.134649093945531</v>
+        <v>1.1884127890505</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1743111678578251</v>
+        <v>-0.2447937859301399</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.905626425385599</v>
+        <v>2.86333685454221</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.796557200518673</v>
+        <v>-4.66214796275625</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.081670530210968</v>
+        <v>1.135434225315938</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1743111678578251</v>
+        <v>-0.2447937859301399</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.89606313401749</v>
+        <v>2.853773563174101</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.827550359847378</v>
+        <v>-4.693141122084955</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8939828315198732</v>
+        <v>0.9477465266248424</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1743111678578251</v>
+        <v>-0.2447937859301399</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.720772699057877</v>
+        <v>2.678483128214488</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.652076100054909</v>
+        <v>-4.517666862292486</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9687397674286484</v>
+        <v>1.022503462533618</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1743111678578251</v>
+        <v>-0.2447937859301399</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.725339931049665</v>
+        <v>2.683050360206276</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.763012352696158</v>
+        <v>-4.628603114933735</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.900107295133356</v>
+        <v>0.9538709902383251</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1743111678578251</v>
+        <v>-0.2447937859301399</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.701081959810872</v>
+        <v>2.658792388967483</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.966038930239391</v>
+        <v>-4.831629692476969</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8220280493359682</v>
+        <v>0.8757917444409373</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3773377454010585</v>
+        <v>-0.4478203634733733</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.582397398504837</v>
+        <v>2.540107827661448</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.808113331304098</v>
+        <v>-4.673704093541676</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8953706753422177</v>
+        <v>0.9491343704471868</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3773377454010585</v>
+        <v>-0.4478203634733733</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.59256978493697</v>
+        <v>2.550280214093581</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.721869868277721</v>
+        <v>-4.587460630515298</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9248143311266293</v>
+        <v>0.9785780262315984</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3773377454010585</v>
+        <v>-0.4478203634733733</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.58751605551083</v>
+        <v>2.545226484667441</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.767176687676701</v>
+        <v>-4.632767449914278</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8984673788115627</v>
+        <v>0.9522310739165318</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4181479084102893</v>
+        <v>-0.4886305264826041</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.554805733149817</v>
+        <v>2.512516162306428</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.796209792379002</v>
+        <v>-4.661800554616579</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.887406009963744</v>
+        <v>0.9411697050687131</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4181479084102893</v>
+        <v>-0.4886305264826041</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.555357606182918</v>
+        <v>2.51306803533953</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.703399310928142</v>
+        <v>-4.568990073165719</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8538028944354534</v>
+        <v>0.9075665895404226</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3253374269594299</v>
+        <v>-0.3958200450317447</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.5403165869448</v>
+        <v>2.498027016101411</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.74778878025757</v>
+        <v>-4.613379542495147</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8379205826282832</v>
+        <v>0.8916842777332523</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3697268962888576</v>
+        <v>-0.4402095143611724</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.515556381271744</v>
+        <v>2.473266810428355</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.635117562021319</v>
+        <v>-4.500708324258897</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8780647784345064</v>
+        <v>0.9318284735394755</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2570556780526074</v>
+        <v>-0.3275382961249222</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.578234820725217</v>
+        <v>2.535945249881828</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.522740560838646</v>
+        <v>-4.388331323076224</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9285068747382428</v>
+        <v>0.9822705698432119</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2570556780526074</v>
+        <v>-0.3275382961249222</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.583726116555884</v>
+        <v>2.541436545712496</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.720975129725377</v>
+        <v>-4.586565891962954</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8607102489520895</v>
+        <v>0.9144739440570586</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.455290246939338</v>
+        <v>-0.5257728650116528</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.476282576992385</v>
+        <v>2.433993006148996</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.803976410750656</v>
+        <v>-4.669567172988233</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6658654565426312</v>
+        <v>0.7196291516476003</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4738611314665117</v>
+        <v>-0.5443437495388266</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.303495766276734</v>
+        <v>2.261206195433345</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.931043417057644</v>
+        <v>-4.796634179295221</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7351883147390414</v>
+        <v>0.7889520098440106</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4738611314665117</v>
+        <v>-0.5443437495388266</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.42364542699594</v>
+        <v>2.381355856152551</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.017642000038747</v>
+        <v>-4.883232762276324</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7150619076489235</v>
+        <v>0.7688256027538924</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4738611314665117</v>
+        <v>-0.5443437495388266</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.438158453098263</v>
+        <v>2.395868882254874</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.979258337480596</v>
+        <v>-4.844849099718173</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7278348140145525</v>
+        <v>0.7815985091195217</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4354774689083605</v>
+        <v>-0.5059600869806754</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.458608091975522</v>
+        <v>2.416318521132133</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.80214200744543</v>
+        <v>-4.667732769683007</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7954103748739207</v>
+        <v>0.8491740699788899</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4354774689083605</v>
+        <v>-0.5059600869806754</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.455337120820824</v>
+        <v>2.413047549977435</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.772439883469136</v>
+        <v>-4.638030645706714</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8079746162263515</v>
+        <v>0.8617383113313206</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4399475941236739</v>
+        <v>-0.5104302121959887</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.453338437453549</v>
+        <v>2.41104886661016</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.593064462230369</v>
+        <v>-4.458655224467946</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8735117600282729</v>
+        <v>0.9272754551332421</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2831708359529552</v>
+        <v>-0.35365345402527</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.541191467662395</v>
+        <v>2.498901896819006</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.638078675750975</v>
+        <v>-4.503669437988552</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.83631352995162</v>
+        <v>0.8900772250565891</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3135197312675598</v>
+        <v>-0.3840023493398746</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.503789585805221</v>
+        <v>2.461500014961833</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.90508318602341</v>
+        <v>-4.770673948260987</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7352032881815918</v>
+        <v>0.7889669832865609</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5078827693105084</v>
+        <v>-0.5783653873828232</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.392863325318398</v>
+        <v>2.350573754475009</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.006280967460583</v>
+        <v>-4.87187172969816</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.693928097503224</v>
+        <v>0.7476917926081932</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5762915828558275</v>
+        <v>-0.6467742009281424</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.351021959087708</v>
+        <v>2.308732388244319</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.973805381289811</v>
+        <v>-4.839396143527388</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7045182935258496</v>
+        <v>0.7582819886308187</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5762915828558275</v>
+        <v>-0.6467742009281424</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.348621920642025</v>
+        <v>2.306332349798636</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.954767253582514</v>
+        <v>-4.820358015820091</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7086582638170134</v>
+        <v>0.7624219589219825</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.634475194187022</v>
+        <v>-0.704957812259337</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.310236473051553</v>
+        <v>2.267946902208164</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.810953543768579</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.985893884733132</v>
+        <v>-4.851484646970709</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8162395655615791</v>
+        <v>0.9275531754004158</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.634475194187022</v>
+        <v>-0.704957812259337</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.430268427256366</v>
+        <v>2.445528771146845</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.811786872754713</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.038214265333924</v>
+        <v>-4.903805027571501</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.796144742307396</v>
+        <v>0.9074583521462327</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5995283341781499</v>
+        <v>-0.6700109522504648</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.452069872247823</v>
+        <v>2.467330216138302</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.817795403151639</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.182537171258843</v>
+        <v>-5.04812793349642</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7444241103343541</v>
+        <v>0.8557377201731908</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5995283341781499</v>
+        <v>-0.6700109522504648</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.458078402644749</v>
+        <v>2.473338746535227</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.89694805094366</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.03479420102384</v>
+        <v>-4.900384963261417</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8826739462203772</v>
+        <v>0.993987556059214</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4317209769432667</v>
+        <v>-0.5022035950155816</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.637915464777701</v>
+        <v>2.653175808668179</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.899741672475141</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.136808883555061</v>
+        <v>-5.002399645792639</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8446616947393695</v>
+        <v>0.9559753045782065</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4317209769432667</v>
+        <v>-0.5022035950155816</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.640709086309182</v>
+        <v>2.65596943019966</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.9004040208668</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.000199539460969</v>
+        <v>-4.865790301698546</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.899967780768665</v>
+        <v>1.011281390607502</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2951116328491742</v>
+        <v>-0.3655942509214892</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.723337041157296</v>
+        <v>2.738597385047774</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.89948449760691</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.142964872283619</v>
+        <v>-5.008555634521196</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8419421243797154</v>
+        <v>0.9532557342185521</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4378769656718247</v>
+        <v>-0.5083595837441396</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.636758318203816</v>
+        <v>2.652018662094294</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.965820051403731</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.080666873507496</v>
+        <v>-4.946257635745074</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.933196877686985</v>
+        <v>1.044510487525822</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4378769656718247</v>
+        <v>-0.5083595837441396</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.703093872000637</v>
+        <v>2.718354215891115</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.674400923793129</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.878876675842339</v>
+        <v>-4.744467438079916</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7224938291424463</v>
+        <v>0.8338074389812831</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2398587735026703</v>
+        <v>-0.3103413915749852</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.530485659691527</v>
+        <v>2.545746003582006</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.744691156115304</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.818985994199745</v>
+        <v>-4.684576756437322</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8167403341216588</v>
+        <v>0.9280539439604956</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1799680918600768</v>
+        <v>-0.2504507099323917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.636710300999258</v>
+        <v>2.651970644889737</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.759318892231348</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.91672653882472</v>
+        <v>-4.782317301062297</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7922718523877128</v>
+        <v>0.9035854622265496</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.195857369993057</v>
+        <v>-0.2663399880653719</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.641804470235514</v>
+        <v>2.657064814125992</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.75785487305602</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.093064298947649</v>
+        <v>-4.958655061185226</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7202727291632125</v>
+        <v>0.8315863390020495</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3721951301159864</v>
+        <v>-0.4426777481883013</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.534537794986428</v>
+        <v>2.549798138876906</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.756346491095948</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.092374926786426</v>
+        <v>-4.957965689024003</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7190400960676304</v>
+        <v>0.8303537059064672</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3721951301159864</v>
+        <v>-0.4426777481883013</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.533029413026357</v>
+        <v>2.548289756916835</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.756209358531384</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.098945891841018</v>
+        <v>-4.964536654078596</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7162745774812298</v>
+        <v>0.8275881873200663</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3787660951705793</v>
+        <v>-0.4492487132428942</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.528949701429037</v>
+        <v>2.544210045319516</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863228</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.756209358531384</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.090991921546246</v>
+        <v>-4.956582683783823</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7194561655991385</v>
+        <v>0.8307697754379753</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3787660951705793</v>
+        <v>-0.4492487132428942</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.528949701429037</v>
+        <v>2.544210045319516</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.762591115559188</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.080618545213159</v>
+        <v>-4.946209307450737</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7299872731601775</v>
+        <v>0.8413008829990147</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.368392718837492</v>
+        <v>-0.438875336909807</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.541555484256694</v>
+        <v>2.556815828147172</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.767483488933913</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.952934235418863</v>
+        <v>-4.81852499765644</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7859533704526207</v>
+        <v>0.8972669802914579</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2407084090431956</v>
+        <v>-0.3111910271155105</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.623058443507996</v>
+        <v>2.638318787398475</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.754238161409786</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.013600825821252</v>
+        <v>-4.879191588058829</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7484414067675376</v>
+        <v>0.8597550166063748</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3224067257617292</v>
+        <v>-0.3928893438340442</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.560794125952748</v>
+        <v>2.576054469843228</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690033</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.758335864020414</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.948606965887606</v>
+        <v>-4.814197728125183</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7785366533516243</v>
+        <v>0.8898502631904615</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2955761111575739</v>
+        <v>-0.3660587292298888</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.58099019732587</v>
+        <v>2.596250541216349</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.749782124634905</v>
+        <v>3.805006858893677</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.492269262914626</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.948606965887606</v>
+        <v>-4.79905739707099</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7785366533516243</v>
+        <v>0.9000673352432169</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2955761111575739</v>
+        <v>-0.3577942664199715</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.485333059900994</v>
+        <v>2.605370158533377</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240601.xlsx
+++ b/tame_output/ON/bt/strategyON_20240601.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.6%</t>
+          <t>450.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.5%</t>
+          <t>-644.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.2%</t>
+          <t>-287.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.6%</t>
+          <t>-152.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-259.8%</t>
+          <t>-280.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-185.5%</t>
+          <t>-198.1%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785791</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.500708324258897</v>
+        <v>-4.649355779901339</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9318284735394755</v>
+        <v>0.8723694912824984</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3275382961249222</v>
+        <v>-0.4761857517673647</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.535945249881828</v>
+        <v>2.446756776496363</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.388331323076224</v>
+        <v>-4.536978778718666</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9822705698432119</v>
+        <v>0.9228115875862348</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3275382961249222</v>
+        <v>-0.4761857517673647</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.541436545712496</v>
+        <v>2.45224807232703</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.586565891962954</v>
+        <v>-4.735213347605397</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9144739440570586</v>
+        <v>0.8550149618000815</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5257728650116528</v>
+        <v>-0.6744203206540953</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.433993006148996</v>
+        <v>2.344804532763531</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.669567172988233</v>
+        <v>-4.818214628630676</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7196291516476003</v>
+        <v>0.6601701693906232</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5443437495388266</v>
+        <v>-0.692991205181269</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.261206195433345</v>
+        <v>2.17201772204788</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.796634179295221</v>
+        <v>-4.945281634937664</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7889520098440106</v>
+        <v>0.7294930275870337</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5443437495388266</v>
+        <v>-0.692991205181269</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.381355856152551</v>
+        <v>2.292167382767085</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.883232762276324</v>
+        <v>-5.031880217918767</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7688256027538924</v>
+        <v>0.7093666204969153</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5443437495388266</v>
+        <v>-0.692991205181269</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.395868882254874</v>
+        <v>2.306680408869408</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.844849099718173</v>
+        <v>-4.993496555360616</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7815985091195217</v>
+        <v>0.7221395268625446</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5059600869806754</v>
+        <v>-0.6546075426231178</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.416318521132133</v>
+        <v>2.327130047746668</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.667732769683007</v>
+        <v>-4.81638022532545</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8491740699788899</v>
+        <v>0.789715087721913</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5059600869806754</v>
+        <v>-0.6546075426231178</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.413047549977435</v>
+        <v>2.32385907659197</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.638030645706714</v>
+        <v>-4.786678101349156</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8617383113313206</v>
+        <v>0.8022793290743435</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5104302121959887</v>
+        <v>-0.6590776678384311</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.41104886661016</v>
+        <v>2.321860393224695</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.458655224467946</v>
+        <v>-4.607302680110388</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9272754551332421</v>
+        <v>0.867816472876265</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.35365345402527</v>
+        <v>-0.5023009096677125</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.498901896819006</v>
+        <v>2.40971342343354</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.503669437988552</v>
+        <v>-4.652316893630994</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8900772250565891</v>
+        <v>0.8306182427996125</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3840023493398746</v>
+        <v>-0.5326498049823171</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.461500014961833</v>
+        <v>2.372311541576368</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.770673948260987</v>
+        <v>-4.919321403903429</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7889669832865609</v>
+        <v>0.7295080010295842</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5783653873828232</v>
+        <v>-0.7270128430252656</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.350573754475009</v>
+        <v>2.261385281089544</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.87187172969816</v>
+        <v>-5.020519185340602</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7476917926081932</v>
+        <v>0.6882328103512165</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6467742009281424</v>
+        <v>-0.7954216565705847</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.308732388244319</v>
+        <v>2.219543914858854</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.839396143527388</v>
+        <v>-4.98804359916983</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7582819886308187</v>
+        <v>0.6988230063738421</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6467742009281424</v>
+        <v>-0.7954216565705847</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.306332349798636</v>
+        <v>2.217143876413171</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.820358015820091</v>
+        <v>-4.969005471462532</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7624219589219825</v>
+        <v>0.7029629766650061</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.704957812259337</v>
+        <v>-0.8536052679017793</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.267946902208164</v>
+        <v>2.178758428822699</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.851484646970709</v>
+        <v>-5.000132102613151</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9275531754004158</v>
+        <v>0.8680941931434392</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.704957812259337</v>
+        <v>-0.8536052679017793</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.445528771146845</v>
+        <v>2.356340297761379</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.903805027571501</v>
+        <v>-5.052452483213942</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9074583521462327</v>
+        <v>0.8479993698892558</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6700109522504648</v>
+        <v>-0.8186584078929071</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.467330216138302</v>
+        <v>2.378141742752836</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.04812793349642</v>
+        <v>-5.196775389138861</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8557377201731908</v>
+        <v>0.7962787379162144</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6700109522504648</v>
+        <v>-0.8186584078929071</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.473338746535227</v>
+        <v>2.384150273149762</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.900384963261417</v>
+        <v>-5.049032418903859</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.993987556059214</v>
+        <v>0.9345285738022375</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5022035950155816</v>
+        <v>-0.650851050658024</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.653175808668179</v>
+        <v>2.563987335282714</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.002399645792639</v>
+        <v>-5.15104710143508</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9559753045782065</v>
+        <v>0.8965163223212298</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5022035950155816</v>
+        <v>-0.650851050658024</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.65596943019966</v>
+        <v>2.566780956814195</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.865790301698546</v>
+        <v>-5.014437757340987</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011281390607502</v>
+        <v>0.9518224083505253</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3655942509214892</v>
+        <v>-0.5142417065639315</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.738597385047774</v>
+        <v>2.649408911662309</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.008555634521196</v>
+        <v>-5.157203090163637</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9532557342185521</v>
+        <v>0.8937967519615753</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5083595837441396</v>
+        <v>-0.6570070393865819</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.652018662094294</v>
+        <v>2.562830188708829</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.946257635745074</v>
+        <v>-5.094905091387515</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.044510487525822</v>
+        <v>0.9850515052688453</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5083595837441396</v>
+        <v>-0.6570070393865819</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.718354215891115</v>
+        <v>2.62916574250565</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.744467438079916</v>
+        <v>-4.893114893722357</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8338074389812831</v>
+        <v>0.7743484567243064</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3103413915749852</v>
+        <v>-0.4589888472174275</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.545746003582006</v>
+        <v>2.456557530196541</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.684576756437322</v>
+        <v>-4.833224212079764</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9280539439604956</v>
+        <v>0.8685949617035189</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2504507099323917</v>
+        <v>-0.399098165574834</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.651970644889737</v>
+        <v>2.562782171504272</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.782317301062297</v>
+        <v>-4.930964756704738</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9035854622265496</v>
+        <v>0.8441264799695729</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2663399880653719</v>
+        <v>-0.4149874437078142</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.657064814125992</v>
+        <v>2.567876340740527</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.958655061185226</v>
+        <v>-5.107302516827668</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8315863390020495</v>
+        <v>0.7721273567450728</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4426777481883013</v>
+        <v>-0.5913252038307436</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.549798138876906</v>
+        <v>2.460609665491441</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.957965689024003</v>
+        <v>-5.106613144666444</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8303537059064672</v>
+        <v>0.7708947236494907</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4426777481883013</v>
+        <v>-0.5913252038307436</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.548289756916835</v>
+        <v>2.45910128353137</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.964536654078596</v>
+        <v>-5.113184109721037</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8275881873200663</v>
+        <v>0.7681292050630897</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4492487132428942</v>
+        <v>-0.5978961688853366</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.544210045319516</v>
+        <v>2.45502157193405</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863228</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.956582683783823</v>
+        <v>-5.105230139426265</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8307697754379753</v>
+        <v>0.7713107931809988</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4492487132428942</v>
+        <v>-0.5978961688853366</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.544210045319516</v>
+        <v>2.45502157193405</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.946209307450737</v>
+        <v>-5.094856763093178</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8413008829990147</v>
+        <v>0.7818419007420379</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.438875336909807</v>
+        <v>-0.5875227925522493</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.556815828147172</v>
+        <v>2.467627354761707</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326881</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.81852499765644</v>
+        <v>-4.967172453298882</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8972669802914579</v>
+        <v>0.8378079980344815</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3111910271155105</v>
+        <v>-0.4598384827579528</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.638318787398475</v>
+        <v>2.54913031401301</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.879191588058829</v>
+        <v>-5.02783904370127</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8597550166063748</v>
+        <v>0.8002960343493983</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3928893438340442</v>
+        <v>-0.5415367994764865</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.576054469843228</v>
+        <v>2.486865996457762</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690033</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.814197728125183</v>
+        <v>-4.962845183767625</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8898502631904615</v>
+        <v>0.830391280933485</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3660587292298888</v>
+        <v>-0.5147061848723311</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.596250541216349</v>
+        <v>2.507062067830884</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.805006858893677</v>
+        <v>3.433157272736566</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.79905739707099</v>
+        <v>-4.823981900514527</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9000673352432169</v>
+        <v>0.8900975338658021</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3577942664199715</v>
+        <v>-0.568817854385528</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.605370158533377</v>
+        <v>2.478756005754044</v>
       </c>
     </row>
   </sheetData>
